--- a/ReportDefs_vervestacks.xlsx
+++ b/ReportDefs_vervestacks.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NZL_grids\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9F22B28-2473-446F-9844-835B9D597BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4971A48D-EA7E-47F9-91E1-254A2F7571D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenMap_OLD" sheetId="70" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2969" uniqueCount="1016">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3175" uniqueCount="1152">
   <si>
     <t>Unit</t>
   </si>
@@ -3132,6 +3132,414 @@
   </si>
   <si>
     <t>NZL-elc_wof_033</t>
+  </si>
+  <si>
+    <t>sect_*</t>
+  </si>
+  <si>
+    <t>PJ</t>
+  </si>
+  <si>
+    <t>Final Energy</t>
+  </si>
+  <si>
+    <t>eu_Aviation</t>
+  </si>
+  <si>
+    <t>Aviation</t>
+  </si>
+  <si>
+    <t>eu_Bus</t>
+  </si>
+  <si>
+    <t>Bus</t>
+  </si>
+  <si>
+    <t>eu_Cars</t>
+  </si>
+  <si>
+    <t>Cars</t>
+  </si>
+  <si>
+    <t>eu_ClothesDry</t>
+  </si>
+  <si>
+    <t>Clothes dry</t>
+  </si>
+  <si>
+    <t>eu_ClothesWash</t>
+  </si>
+  <si>
+    <t>Clothes wash</t>
+  </si>
+  <si>
+    <t>eu_Cooking</t>
+  </si>
+  <si>
+    <t>Cooking</t>
+  </si>
+  <si>
+    <t>eu_DishWash</t>
+  </si>
+  <si>
+    <t>Dish Wash</t>
+  </si>
+  <si>
+    <t>eu_Irrigation</t>
+  </si>
+  <si>
+    <t>Irrigation</t>
+  </si>
+  <si>
+    <t>eu_Lighting</t>
+  </si>
+  <si>
+    <t>Lighting</t>
+  </si>
+  <si>
+    <t>eu_MotivePower</t>
+  </si>
+  <si>
+    <t>Motive Power</t>
+  </si>
+  <si>
+    <t>eu_Motorcycle</t>
+  </si>
+  <si>
+    <t>Motorcycle</t>
+  </si>
+  <si>
+    <t>eu_ProcessHeat</t>
+  </si>
+  <si>
+    <t>Process Heat</t>
+  </si>
+  <si>
+    <t>eu_Pumping</t>
+  </si>
+  <si>
+    <t>Pumping</t>
+  </si>
+  <si>
+    <t>eu_Rail</t>
+  </si>
+  <si>
+    <t>Rail</t>
+  </si>
+  <si>
+    <t>eu_Refrigeration</t>
+  </si>
+  <si>
+    <t>Refrigeration</t>
+  </si>
+  <si>
+    <t>eu_Ships</t>
+  </si>
+  <si>
+    <t>Ships</t>
+  </si>
+  <si>
+    <t>eu_SpaceCool</t>
+  </si>
+  <si>
+    <t>Space Cool</t>
+  </si>
+  <si>
+    <t>eu_SpaceHeat</t>
+  </si>
+  <si>
+    <t>Space Heat</t>
+  </si>
+  <si>
+    <t>eu_Trucks</t>
+  </si>
+  <si>
+    <t>Trucks</t>
+  </si>
+  <si>
+    <t>eu_WaterHeat</t>
+  </si>
+  <si>
+    <t>Water Heat</t>
+  </si>
+  <si>
+    <t>s_Agriculture</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>s_BioProc</t>
+  </si>
+  <si>
+    <t>Bio Processing</t>
+  </si>
+  <si>
+    <t>s_Commercial</t>
+  </si>
+  <si>
+    <t>Commercial</t>
+  </si>
+  <si>
+    <t>s_Hydrogen</t>
+  </si>
+  <si>
+    <t>Hydrogen Prod</t>
+  </si>
+  <si>
+    <t>s_Industry</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>s_Power</t>
+  </si>
+  <si>
+    <t>s_PriExp</t>
+  </si>
+  <si>
+    <t>Primary Exports</t>
+  </si>
+  <si>
+    <t>s_PriImp</t>
+  </si>
+  <si>
+    <t>Primary Imports</t>
+  </si>
+  <si>
+    <t>s_PriProd</t>
+  </si>
+  <si>
+    <t>Primary Production</t>
+  </si>
+  <si>
+    <t>s_Refinery</t>
+  </si>
+  <si>
+    <t>Refinery</t>
+  </si>
+  <si>
+    <t>s_Residential</t>
+  </si>
+  <si>
+    <t>Residential</t>
+  </si>
+  <si>
+    <t>s_Storage</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>s_Transport</t>
+  </si>
+  <si>
+    <t>Transport</t>
+  </si>
+  <si>
+    <t>ss_Attached</t>
+  </si>
+  <si>
+    <t>Attached</t>
+  </si>
+  <si>
+    <t>ss_Chemicals</t>
+  </si>
+  <si>
+    <t>Chemicals</t>
+  </si>
+  <si>
+    <t>ss_Construction</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>ss_Dairy</t>
+  </si>
+  <si>
+    <t>Dairy</t>
+  </si>
+  <si>
+    <t>ss_DairyCattleFarming</t>
+  </si>
+  <si>
+    <t>Dairy Cattle Farming</t>
+  </si>
+  <si>
+    <t>ss_Detached</t>
+  </si>
+  <si>
+    <t>Detached</t>
+  </si>
+  <si>
+    <t>ss_Education</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>ss_Fishing</t>
+  </si>
+  <si>
+    <t>Fishing</t>
+  </si>
+  <si>
+    <t>ss_Food</t>
+  </si>
+  <si>
+    <t>Food</t>
+  </si>
+  <si>
+    <t>ss_Forestry</t>
+  </si>
+  <si>
+    <t>Forestry</t>
+  </si>
+  <si>
+    <t>ss_Healthcare</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>ss_Horticulture</t>
+  </si>
+  <si>
+    <t>Horticulture</t>
+  </si>
+  <si>
+    <t>ss_Indoorcropping</t>
+  </si>
+  <si>
+    <t>Indoor cropping</t>
+  </si>
+  <si>
+    <t>ss_Livestock</t>
+  </si>
+  <si>
+    <t>Livestock</t>
+  </si>
+  <si>
+    <t>ss_Meat</t>
+  </si>
+  <si>
+    <t>Meat</t>
+  </si>
+  <si>
+    <t>ss_Metals</t>
+  </si>
+  <si>
+    <t>Metals</t>
+  </si>
+  <si>
+    <t>ss_Methanol</t>
+  </si>
+  <si>
+    <t>Methanol</t>
+  </si>
+  <si>
+    <t>ss_Minerals</t>
+  </si>
+  <si>
+    <t>Minerals</t>
+  </si>
+  <si>
+    <t>ss_Mining</t>
+  </si>
+  <si>
+    <t>Mining</t>
+  </si>
+  <si>
+    <t>ss_Office</t>
+  </si>
+  <si>
+    <t>Office</t>
+  </si>
+  <si>
+    <t>ss_OtherInd</t>
+  </si>
+  <si>
+    <t>Other Ind</t>
+  </si>
+  <si>
+    <t>ss_OtherAgri</t>
+  </si>
+  <si>
+    <t>Other Agri</t>
+  </si>
+  <si>
+    <t>ss_OtherCom</t>
+  </si>
+  <si>
+    <t>Other Com</t>
+  </si>
+  <si>
+    <t>ss_Paper</t>
+  </si>
+  <si>
+    <t>Paper</t>
+  </si>
+  <si>
+    <t>ss_Refining</t>
+  </si>
+  <si>
+    <t>Refining</t>
+  </si>
+  <si>
+    <t>ss_Steel</t>
+  </si>
+  <si>
+    <t>Steel</t>
+  </si>
+  <si>
+    <t>ss_Urea</t>
+  </si>
+  <si>
+    <t>Urea</t>
+  </si>
+  <si>
+    <t>ss_WoodProdMfg</t>
+  </si>
+  <si>
+    <t>Wood Prod Mfg</t>
+  </si>
+  <si>
+    <t>ss_WSR</t>
+  </si>
+  <si>
+    <t>WSR</t>
+  </si>
+  <si>
+    <t>enduse</t>
+  </si>
+  <si>
+    <t>commercial</t>
+  </si>
+  <si>
+    <t>COM*</t>
+  </si>
+  <si>
+    <t>residential</t>
+  </si>
+  <si>
+    <t>RES*</t>
+  </si>
+  <si>
+    <t>IND*</t>
+  </si>
+  <si>
+    <t>agriculture</t>
+  </si>
+  <si>
+    <t>AGR*</t>
+  </si>
+  <si>
+    <t>TRA*</t>
+  </si>
+  <si>
+    <t>sector</t>
   </si>
 </sst>
 </file>
@@ -5964,7 +6372,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10ADB714-E6AA-4E3E-B77B-62B65BA0E218}">
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.86328125" bestFit="1" customWidth="1"/>
@@ -6742,7 +7150,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:5">
       <c r="A65" t="s">
         <v>402</v>
       </c>
@@ -6753,7 +7161,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:5">
       <c r="A66" t="s">
         <v>402</v>
       </c>
@@ -6762,6 +7170,743 @@
       </c>
       <c r="C66" t="s">
         <v>414</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E67" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E68" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C69" t="s">
+        <v>189</v>
+      </c>
+      <c r="E69" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C70" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E70" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C71" t="s">
+        <v>190</v>
+      </c>
+      <c r="E71" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D72" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D73" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D74" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D75" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D76" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D77" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D78" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D79" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D80" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D81" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C82" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D82" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C83" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D83" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D84" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C85" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D85" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D86" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D87" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C88" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D88" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C89" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D89" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C90" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D90" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C91" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D91" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C92" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D92" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C93" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D93" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C94" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D94" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D95" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C96" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D96" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C97" t="s">
+        <v>42</v>
+      </c>
+      <c r="D97" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C98" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D98" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C99" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D99" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C100" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D100" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C101" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D101" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C102" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D102" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D103" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C104" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D104" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C105" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D105" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C106" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D106" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C107" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D107" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C108" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D108" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C109" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D109" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C110" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D110" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C111" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D111" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C112" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D112" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C113" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D113" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C114" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D114" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C115" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D115" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C116" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D116" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C117" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D117" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C118" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D118" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C119" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D119" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C120" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D120" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C121" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D121" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C122" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D122" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C123" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D123" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C124" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D124" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C125" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D125" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C126" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D126" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C127" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D127" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C128" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D128" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C129" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D129" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C130" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D130" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C131" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D131" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C132" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D132" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C133" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D133" t="s">
+        <v>1140</v>
       </c>
     </row>
   </sheetData>
@@ -19199,7 +20344,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:U22"/>
+  <dimension ref="A1:U23"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.86328125" bestFit="1" customWidth="1"/>
@@ -19665,6 +20810,23 @@
         <v>44</v>
       </c>
     </row>
+    <row r="23" spans="1:17">
+      <c r="A23" t="s">
+        <v>161</v>
+      </c>
+      <c r="H23" t="s">
+        <v>1016</v>
+      </c>
+      <c r="K23" t="s">
+        <v>1017</v>
+      </c>
+      <c r="N23" t="s">
+        <v>1018</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>399</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="T4:U4"/>

--- a/ReportDefs_vervestacks.xlsx
+++ b/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2948FC9-95BB-4921-983A-5AF8EBDC3A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5049DA-4A1C-4846-AA89-387D28D5F3B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenMap_OLD" sheetId="70" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3160" uniqueCount="1144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3271" uniqueCount="1212">
   <si>
     <t>Unit</t>
   </si>
@@ -3516,6 +3516,210 @@
   </si>
   <si>
     <t>*CO2,-TOT*</t>
+  </si>
+  <si>
+    <t>nrg_COA</t>
+  </si>
+  <si>
+    <t>Coal</t>
+  </si>
+  <si>
+    <t>nrg_DSL</t>
+  </si>
+  <si>
+    <t>Diesel</t>
+  </si>
+  <si>
+    <t>nrg_ELC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electricity </t>
+  </si>
+  <si>
+    <t>nrg_FOL</t>
+  </si>
+  <si>
+    <t>Fuel Oil</t>
+  </si>
+  <si>
+    <t>nrg_GEO</t>
+  </si>
+  <si>
+    <t>Geothermal</t>
+  </si>
+  <si>
+    <t>nrg_H2R</t>
+  </si>
+  <si>
+    <t>nrg_LPG</t>
+  </si>
+  <si>
+    <t>LPG</t>
+  </si>
+  <si>
+    <t>nrg_NGA</t>
+  </si>
+  <si>
+    <t>Natural Gas</t>
+  </si>
+  <si>
+    <t>nrg_PET</t>
+  </si>
+  <si>
+    <t>Petrol</t>
+  </si>
+  <si>
+    <t>nrg_PLT</t>
+  </si>
+  <si>
+    <t>Pellet</t>
+  </si>
+  <si>
+    <t>nrg_WOD</t>
+  </si>
+  <si>
+    <t>Wood</t>
+  </si>
+  <si>
+    <t>nrg_WST</t>
+  </si>
+  <si>
+    <t>Waste</t>
+  </si>
+  <si>
+    <t>nrg_MNR</t>
+  </si>
+  <si>
+    <t>Manure</t>
+  </si>
+  <si>
+    <t>nrg_BIG</t>
+  </si>
+  <si>
+    <t>Biogas</t>
+  </si>
+  <si>
+    <t>nrg_BIL</t>
+  </si>
+  <si>
+    <t>Bioliquid</t>
+  </si>
+  <si>
+    <t>nrg_COL</t>
+  </si>
+  <si>
+    <t>Lignite</t>
+  </si>
+  <si>
+    <t>nrg_seq</t>
+  </si>
+  <si>
+    <t>CO2 to CCS</t>
+  </si>
+  <si>
+    <t>nrg_CO2</t>
+  </si>
+  <si>
+    <t>CO2</t>
+  </si>
+  <si>
+    <t>nrg_DID</t>
+  </si>
+  <si>
+    <t>Drop-In Diesel</t>
+  </si>
+  <si>
+    <t>nrg_DIJ</t>
+  </si>
+  <si>
+    <t>Drop-In Jet</t>
+  </si>
+  <si>
+    <t>nrg_LCD</t>
+  </si>
+  <si>
+    <t>Electricity Production</t>
+  </si>
+  <si>
+    <t>nrg_CDD</t>
+  </si>
+  <si>
+    <t>nrg_-HV</t>
+  </si>
+  <si>
+    <t>nrg_HYD</t>
+  </si>
+  <si>
+    <t>Hydro</t>
+  </si>
+  <si>
+    <t>nrg_-MV</t>
+  </si>
+  <si>
+    <t>nrg_OIL</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
+  <si>
+    <t>nrg_SOL</t>
+  </si>
+  <si>
+    <t>nrg_TID</t>
+  </si>
+  <si>
+    <t>Tidal</t>
+  </si>
+  <si>
+    <t>nrg_URN</t>
+  </si>
+  <si>
+    <t>Uranium</t>
+  </si>
+  <si>
+    <t>nrg_WIN</t>
+  </si>
+  <si>
+    <t>nrg_H2C</t>
+  </si>
+  <si>
+    <t>nrg_H2D</t>
+  </si>
+  <si>
+    <t>nrg_JET</t>
+  </si>
+  <si>
+    <t>Jet Fuel</t>
+  </si>
+  <si>
+    <t>nrg_LNG</t>
+  </si>
+  <si>
+    <t>LNG</t>
+  </si>
+  <si>
+    <t>nrg_ILD</t>
+  </si>
+  <si>
+    <t>Crude Oil (domestic)</t>
+  </si>
+  <si>
+    <t>nrg_ILI</t>
+  </si>
+  <si>
+    <t>Crude Oil (imported)</t>
+  </si>
+  <si>
+    <t>nrg_OTH</t>
+  </si>
+  <si>
+    <t>Other Oil</t>
+  </si>
+  <si>
+    <t>fuel</t>
+  </si>
+  <si>
+    <t>Green Hydrogen Fuel</t>
   </si>
 </sst>
 </file>
@@ -7840,17 +8044,17 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE3245E1-8745-41DD-8AE6-2F4FA19D9F1C}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="13.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.73046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.86328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.73046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.86328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -7882,6 +8086,413 @@
       </c>
       <c r="H2" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C8" t="s">
+        <v>275</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D27" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C29" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D31" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C32" t="s">
+        <v>102</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D37" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D38" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1208</v>
       </c>
     </row>
   </sheetData>

--- a/ReportDefs_vervestacks.xlsx
+++ b/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5049DA-4A1C-4846-AA89-387D28D5F3B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027CE7CB-80BD-4CCE-BF53-D2903CD42A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenMap_OLD" sheetId="70" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3271" uniqueCount="1212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3272" uniqueCount="1213">
   <si>
     <t>Unit</t>
   </si>
@@ -3720,6 +3720,9 @@
   </si>
   <si>
     <t>Green Hydrogen Fuel</t>
+  </si>
+  <si>
+    <t>-ev_bat*</t>
   </si>
 </sst>
 </file>
@@ -21349,6 +21352,9 @@
       <c r="A23" t="s">
         <v>160</v>
       </c>
+      <c r="D23" s="2" t="s">
+        <v>1212</v>
+      </c>
       <c r="H23" t="s">
         <v>1015</v>
       </c>

--- a/ReportDefs_vervestacks.xlsx
+++ b/ReportDefs_vervestacks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027CE7CB-80BD-4CCE-BF53-D2903CD42A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B961AF-8DED-46B4-BEF5-DEEDED4A9308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3272" uniqueCount="1213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3283" uniqueCount="1220">
   <si>
     <t>Unit</t>
   </si>
@@ -3723,6 +3723,27 @@
   </si>
   <si>
     <t>-ev_bat*</t>
+  </si>
+  <si>
+    <t>t*car,t*trk</t>
+  </si>
+  <si>
+    <t>000veh</t>
+  </si>
+  <si>
+    <t>T*</t>
+  </si>
+  <si>
+    <t>Tra_vehicles</t>
+  </si>
+  <si>
+    <t>DEM</t>
+  </si>
+  <si>
+    <t>bvkm</t>
+  </si>
+  <si>
+    <t>Tra_bvkm</t>
   </si>
 </sst>
 </file>
@@ -20882,7 +20903,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:U23"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.86328125" bestFit="1" customWidth="1"/>
@@ -21368,6 +21389,43 @@
         <v>398</v>
       </c>
     </row>
+    <row r="24" spans="1:17">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1215</v>
+      </c>
+      <c r="G24" t="s">
+        <v>1213</v>
+      </c>
+      <c r="K24" t="s">
+        <v>1214</v>
+      </c>
+      <c r="N24" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1215</v>
+      </c>
+      <c r="G25" t="s">
+        <v>1213</v>
+      </c>
+      <c r="H25" t="s">
+        <v>1217</v>
+      </c>
+      <c r="K25" t="s">
+        <v>1218</v>
+      </c>
+      <c r="N25" t="s">
+        <v>1219</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="T4:U4"/>

--- a/ReportDefs_vervestacks.xlsx
+++ b/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B961AF-8DED-46B4-BEF5-DEEDED4A9308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3499473B-CB2E-4D3F-BC33-E5764E691F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3283" uniqueCount="1220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3285" uniqueCount="1220">
   <si>
     <t>Unit</t>
   </si>
@@ -21405,6 +21405,9 @@
       <c r="N24" t="s">
         <v>1216</v>
       </c>
+      <c r="Q24" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="25" spans="1:17">
       <c r="A25" t="s">
@@ -21424,6 +21427,9 @@
       </c>
       <c r="N25" t="s">
         <v>1219</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/ReportDefs_vervestacks.xlsx
+++ b/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3499473B-CB2E-4D3F-BC33-E5764E691F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B68A07F-32F9-49DA-81AF-AD0A1580B9BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" firstSheet="2" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenMap_OLD" sheetId="70" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3285" uniqueCount="1220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3305" uniqueCount="1229">
   <si>
     <t>Unit</t>
   </si>
@@ -3744,6 +3744,33 @@
   </si>
   <si>
     <t>Tra_bvkm</t>
+  </si>
+  <si>
+    <t>*ICE*</t>
+  </si>
+  <si>
+    <t>*HYB*</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>T[_]*</t>
+  </si>
+  <si>
+    <t>*PHEV*</t>
+  </si>
+  <si>
+    <t>Plug-in Hyb</t>
+  </si>
+  <si>
+    <t>*BEV*</t>
+  </si>
+  <si>
+    <t>Batt EV</t>
+  </si>
+  <si>
+    <t>*FCH*</t>
   </si>
 </sst>
 </file>
@@ -6576,7 +6603,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10ADB714-E6AA-4E3E-B77B-62B65BA0E218}">
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.86328125" bestFit="1" customWidth="1"/>
@@ -7165,7 +7192,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>69</v>
       </c>
@@ -7177,7 +7204,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>69</v>
       </c>
@@ -7191,7 +7218,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>69</v>
       </c>
@@ -7205,7 +7232,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
         <v>69</v>
       </c>
@@ -7219,7 +7246,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>69</v>
       </c>
@@ -7233,7 +7260,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>69</v>
       </c>
@@ -7244,7 +7271,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>69</v>
       </c>
@@ -7255,7 +7282,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>69</v>
       </c>
@@ -7266,92 +7293,107 @@
         <v>114</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
+        <v>69</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C57" t="s">
+        <v>88</v>
+      </c>
+      <c r="F57" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" t="s">
+        <v>69</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F58" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" t="s">
+        <v>69</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F59" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" t="s">
+        <v>69</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F60" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C61" t="s">
+        <v>275</v>
+      </c>
+      <c r="F61" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" t="s">
         <v>391</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B62" t="s">
         <v>392</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C62" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
-      <c r="A58" t="s">
+    <row r="63" spans="1:6">
+      <c r="A63" t="s">
         <v>391</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B63" t="s">
         <v>394</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C63" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
-      <c r="A59" t="s">
+    <row r="64" spans="1:6">
+      <c r="A64" t="s">
         <v>391</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B64" t="s">
         <v>395</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C64" t="s">
         <v>275</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" t="s">
-        <v>401</v>
-      </c>
-      <c r="B60" t="s">
-        <v>120</v>
-      </c>
-      <c r="C60" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" t="s">
-        <v>401</v>
-      </c>
-      <c r="B61" t="s">
-        <v>402</v>
-      </c>
-      <c r="C61" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" t="s">
-        <v>401</v>
-      </c>
-      <c r="B62" t="s">
-        <v>404</v>
-      </c>
-      <c r="C62" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" t="s">
-        <v>401</v>
-      </c>
-      <c r="B63" t="s">
-        <v>406</v>
-      </c>
-      <c r="C63" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" t="s">
-        <v>401</v>
-      </c>
-      <c r="B64" t="s">
-        <v>408</v>
-      </c>
-      <c r="C64" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -7359,10 +7401,10 @@
         <v>401</v>
       </c>
       <c r="B65" t="s">
-        <v>410</v>
+        <v>120</v>
       </c>
       <c r="C65" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -7370,65 +7412,65 @@
         <v>401</v>
       </c>
       <c r="B66" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="C66" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>1141</v>
+        <v>401</v>
+      </c>
+      <c r="B67" t="s">
+        <v>404</v>
       </c>
       <c r="C67" t="s">
-        <v>1019</v>
-      </c>
-      <c r="D67" t="s">
-        <v>1018</v>
+        <v>405</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>1141</v>
+        <v>401</v>
+      </c>
+      <c r="B68" t="s">
+        <v>406</v>
       </c>
       <c r="C68" t="s">
-        <v>1021</v>
-      </c>
-      <c r="D68" t="s">
-        <v>1020</v>
+        <v>407</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>1141</v>
+        <v>401</v>
+      </c>
+      <c r="B69" t="s">
+        <v>408</v>
       </c>
       <c r="C69" t="s">
-        <v>1023</v>
-      </c>
-      <c r="D69" t="s">
-        <v>1022</v>
+        <v>409</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>1141</v>
+        <v>401</v>
+      </c>
+      <c r="B70" t="s">
+        <v>410</v>
       </c>
       <c r="C70" t="s">
-        <v>1025</v>
-      </c>
-      <c r="D70" t="s">
-        <v>1024</v>
+        <v>411</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>1141</v>
+        <v>401</v>
+      </c>
+      <c r="B71" t="s">
+        <v>412</v>
       </c>
       <c r="C71" t="s">
-        <v>1027</v>
-      </c>
-      <c r="D71" t="s">
-        <v>1026</v>
+        <v>413</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -7436,10 +7478,10 @@
         <v>1141</v>
       </c>
       <c r="C72" t="s">
-        <v>1029</v>
+        <v>1019</v>
       </c>
       <c r="D72" t="s">
-        <v>1028</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -7447,10 +7489,10 @@
         <v>1141</v>
       </c>
       <c r="C73" t="s">
-        <v>1031</v>
+        <v>1021</v>
       </c>
       <c r="D73" t="s">
-        <v>1030</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -7458,10 +7500,10 @@
         <v>1141</v>
       </c>
       <c r="C74" t="s">
-        <v>1033</v>
+        <v>1023</v>
       </c>
       <c r="D74" t="s">
-        <v>1032</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -7469,10 +7511,10 @@
         <v>1141</v>
       </c>
       <c r="C75" t="s">
-        <v>1035</v>
+        <v>1025</v>
       </c>
       <c r="D75" t="s">
-        <v>1034</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -7480,10 +7522,10 @@
         <v>1141</v>
       </c>
       <c r="C76" t="s">
-        <v>1037</v>
+        <v>1027</v>
       </c>
       <c r="D76" t="s">
-        <v>1036</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -7491,10 +7533,10 @@
         <v>1141</v>
       </c>
       <c r="C77" t="s">
-        <v>1039</v>
+        <v>1029</v>
       </c>
       <c r="D77" t="s">
-        <v>1038</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -7502,10 +7544,10 @@
         <v>1141</v>
       </c>
       <c r="C78" t="s">
-        <v>1041</v>
+        <v>1031</v>
       </c>
       <c r="D78" t="s">
-        <v>1040</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -7513,10 +7555,10 @@
         <v>1141</v>
       </c>
       <c r="C79" t="s">
-        <v>1043</v>
+        <v>1033</v>
       </c>
       <c r="D79" t="s">
-        <v>1042</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -7524,10 +7566,10 @@
         <v>1141</v>
       </c>
       <c r="C80" t="s">
-        <v>1045</v>
+        <v>1035</v>
       </c>
       <c r="D80" t="s">
-        <v>1044</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -7535,10 +7577,10 @@
         <v>1141</v>
       </c>
       <c r="C81" t="s">
-        <v>1047</v>
+        <v>1037</v>
       </c>
       <c r="D81" t="s">
-        <v>1046</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -7546,10 +7588,10 @@
         <v>1141</v>
       </c>
       <c r="C82" t="s">
-        <v>1049</v>
+        <v>1039</v>
       </c>
       <c r="D82" t="s">
-        <v>1048</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -7557,10 +7599,10 @@
         <v>1141</v>
       </c>
       <c r="C83" t="s">
-        <v>1051</v>
+        <v>1041</v>
       </c>
       <c r="D83" t="s">
-        <v>1050</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -7568,10 +7610,10 @@
         <v>1141</v>
       </c>
       <c r="C84" t="s">
-        <v>1053</v>
+        <v>1043</v>
       </c>
       <c r="D84" t="s">
-        <v>1052</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -7579,10 +7621,10 @@
         <v>1141</v>
       </c>
       <c r="C85" t="s">
-        <v>1055</v>
+        <v>1045</v>
       </c>
       <c r="D85" t="s">
-        <v>1054</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -7590,65 +7632,65 @@
         <v>1141</v>
       </c>
       <c r="C86" t="s">
-        <v>1057</v>
+        <v>1047</v>
       </c>
       <c r="D86" t="s">
-        <v>1056</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>391</v>
+        <v>1141</v>
       </c>
       <c r="C87" t="s">
-        <v>1059</v>
+        <v>1049</v>
       </c>
       <c r="D87" t="s">
-        <v>1058</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>391</v>
+        <v>1141</v>
       </c>
       <c r="C88" t="s">
-        <v>1061</v>
+        <v>1051</v>
       </c>
       <c r="D88" t="s">
-        <v>1060</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>391</v>
+        <v>1141</v>
       </c>
       <c r="C89" t="s">
-        <v>1063</v>
+        <v>1053</v>
       </c>
       <c r="D89" t="s">
-        <v>1062</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>391</v>
+        <v>1141</v>
       </c>
       <c r="C90" t="s">
-        <v>1065</v>
+        <v>1055</v>
       </c>
       <c r="D90" t="s">
-        <v>1064</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>391</v>
+        <v>1141</v>
       </c>
       <c r="C91" t="s">
-        <v>1067</v>
+        <v>1057</v>
       </c>
       <c r="D91" t="s">
-        <v>1066</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -7656,10 +7698,10 @@
         <v>391</v>
       </c>
       <c r="C92" t="s">
-        <v>42</v>
+        <v>1059</v>
       </c>
       <c r="D92" t="s">
-        <v>1068</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -7667,10 +7709,10 @@
         <v>391</v>
       </c>
       <c r="C93" t="s">
-        <v>1070</v>
+        <v>1061</v>
       </c>
       <c r="D93" t="s">
-        <v>1069</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -7678,10 +7720,10 @@
         <v>391</v>
       </c>
       <c r="C94" t="s">
-        <v>1072</v>
+        <v>1063</v>
       </c>
       <c r="D94" t="s">
-        <v>1071</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -7689,10 +7731,10 @@
         <v>391</v>
       </c>
       <c r="C95" t="s">
-        <v>1074</v>
+        <v>1065</v>
       </c>
       <c r="D95" t="s">
-        <v>1073</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -7700,10 +7742,10 @@
         <v>391</v>
       </c>
       <c r="C96" t="s">
-        <v>1076</v>
+        <v>1067</v>
       </c>
       <c r="D96" t="s">
-        <v>1075</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -7711,10 +7753,10 @@
         <v>391</v>
       </c>
       <c r="C97" t="s">
-        <v>1078</v>
+        <v>42</v>
       </c>
       <c r="D97" t="s">
-        <v>1077</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -7722,10 +7764,10 @@
         <v>391</v>
       </c>
       <c r="C98" t="s">
-        <v>1080</v>
+        <v>1070</v>
       </c>
       <c r="D98" t="s">
-        <v>1079</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -7733,65 +7775,65 @@
         <v>391</v>
       </c>
       <c r="C99" t="s">
-        <v>1082</v>
+        <v>1072</v>
       </c>
       <c r="D99" t="s">
-        <v>1081</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>1142</v>
+        <v>391</v>
       </c>
       <c r="C100" t="s">
-        <v>1084</v>
+        <v>1074</v>
       </c>
       <c r="D100" t="s">
-        <v>1083</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>1142</v>
+        <v>391</v>
       </c>
       <c r="C101" t="s">
-        <v>1086</v>
+        <v>1076</v>
       </c>
       <c r="D101" t="s">
-        <v>1085</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>1142</v>
+        <v>391</v>
       </c>
       <c r="C102" t="s">
-        <v>1088</v>
+        <v>1078</v>
       </c>
       <c r="D102" t="s">
-        <v>1087</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>1142</v>
+        <v>391</v>
       </c>
       <c r="C103" t="s">
-        <v>1090</v>
+        <v>1080</v>
       </c>
       <c r="D103" t="s">
-        <v>1089</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>1142</v>
+        <v>391</v>
       </c>
       <c r="C104" t="s">
-        <v>1092</v>
+        <v>1082</v>
       </c>
       <c r="D104" t="s">
-        <v>1091</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -7799,10 +7841,10 @@
         <v>1142</v>
       </c>
       <c r="C105" t="s">
-        <v>1094</v>
+        <v>1084</v>
       </c>
       <c r="D105" t="s">
-        <v>1093</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -7810,10 +7852,10 @@
         <v>1142</v>
       </c>
       <c r="C106" t="s">
-        <v>1096</v>
+        <v>1086</v>
       </c>
       <c r="D106" t="s">
-        <v>1095</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -7821,10 +7863,10 @@
         <v>1142</v>
       </c>
       <c r="C107" t="s">
-        <v>1098</v>
+        <v>1088</v>
       </c>
       <c r="D107" t="s">
-        <v>1097</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -7832,10 +7874,10 @@
         <v>1142</v>
       </c>
       <c r="C108" t="s">
-        <v>1100</v>
+        <v>1090</v>
       </c>
       <c r="D108" t="s">
-        <v>1099</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -7843,10 +7885,10 @@
         <v>1142</v>
       </c>
       <c r="C109" t="s">
-        <v>1102</v>
+        <v>1092</v>
       </c>
       <c r="D109" t="s">
-        <v>1101</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -7854,10 +7896,10 @@
         <v>1142</v>
       </c>
       <c r="C110" t="s">
-        <v>1104</v>
+        <v>1094</v>
       </c>
       <c r="D110" t="s">
-        <v>1103</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -7865,10 +7907,10 @@
         <v>1142</v>
       </c>
       <c r="C111" t="s">
-        <v>1106</v>
+        <v>1096</v>
       </c>
       <c r="D111" t="s">
-        <v>1105</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -7876,10 +7918,10 @@
         <v>1142</v>
       </c>
       <c r="C112" t="s">
-        <v>1108</v>
+        <v>1098</v>
       </c>
       <c r="D112" t="s">
-        <v>1107</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -7887,10 +7929,10 @@
         <v>1142</v>
       </c>
       <c r="C113" t="s">
-        <v>1110</v>
+        <v>1100</v>
       </c>
       <c r="D113" t="s">
-        <v>1109</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -7898,10 +7940,10 @@
         <v>1142</v>
       </c>
       <c r="C114" t="s">
-        <v>1112</v>
+        <v>1102</v>
       </c>
       <c r="D114" t="s">
-        <v>1111</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -7909,10 +7951,10 @@
         <v>1142</v>
       </c>
       <c r="C115" t="s">
-        <v>1114</v>
+        <v>1104</v>
       </c>
       <c r="D115" t="s">
-        <v>1113</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -7920,10 +7962,10 @@
         <v>1142</v>
       </c>
       <c r="C116" t="s">
-        <v>1116</v>
+        <v>1106</v>
       </c>
       <c r="D116" t="s">
-        <v>1115</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -7931,10 +7973,10 @@
         <v>1142</v>
       </c>
       <c r="C117" t="s">
-        <v>1118</v>
+        <v>1108</v>
       </c>
       <c r="D117" t="s">
-        <v>1117</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -7942,10 +7984,10 @@
         <v>1142</v>
       </c>
       <c r="C118" t="s">
-        <v>1120</v>
+        <v>1110</v>
       </c>
       <c r="D118" t="s">
-        <v>1119</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -7953,10 +7995,10 @@
         <v>1142</v>
       </c>
       <c r="C119" t="s">
-        <v>1122</v>
+        <v>1112</v>
       </c>
       <c r="D119" t="s">
-        <v>1121</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -7964,10 +8006,10 @@
         <v>1142</v>
       </c>
       <c r="C120" t="s">
-        <v>1126</v>
+        <v>1114</v>
       </c>
       <c r="D120" t="s">
-        <v>1125</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -7975,10 +8017,10 @@
         <v>1142</v>
       </c>
       <c r="C121" t="s">
-        <v>1128</v>
+        <v>1116</v>
       </c>
       <c r="D121" t="s">
-        <v>1127</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -7986,10 +8028,10 @@
         <v>1142</v>
       </c>
       <c r="C122" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="D122" t="s">
-        <v>1123</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -7997,10 +8039,10 @@
         <v>1142</v>
       </c>
       <c r="C123" t="s">
-        <v>1130</v>
+        <v>1120</v>
       </c>
       <c r="D123" t="s">
-        <v>1129</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -8008,10 +8050,10 @@
         <v>1142</v>
       </c>
       <c r="C124" t="s">
-        <v>1132</v>
+        <v>1122</v>
       </c>
       <c r="D124" t="s">
-        <v>1131</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -8019,10 +8061,10 @@
         <v>1142</v>
       </c>
       <c r="C125" t="s">
-        <v>1134</v>
+        <v>1126</v>
       </c>
       <c r="D125" t="s">
-        <v>1133</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -8030,10 +8072,10 @@
         <v>1142</v>
       </c>
       <c r="C126" t="s">
-        <v>1136</v>
+        <v>1128</v>
       </c>
       <c r="D126" t="s">
-        <v>1135</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -8041,10 +8083,10 @@
         <v>1142</v>
       </c>
       <c r="C127" t="s">
-        <v>1138</v>
+        <v>1124</v>
       </c>
       <c r="D127" t="s">
-        <v>1137</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -8052,15 +8094,70 @@
         <v>1142</v>
       </c>
       <c r="C128" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D128" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C129" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D129" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C130" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D130" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C131" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D131" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C132" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D132" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C133" t="s">
         <v>1140</v>
       </c>
-      <c r="D128" t="s">
+      <c r="D133" t="s">
         <v>1139</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A67:D128">
-    <sortCondition ref="D67:D128"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A72:D133">
+    <sortCondition ref="D72:D133"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ReportDefs_vervestacks.xlsx
+++ b/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D9506C-756B-4030-B830-016848E46BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF629D7-6FA6-4F85-8743-2F2305CE80E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33098" yWindow="1958" windowWidth="21600" windowHeight="12682" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenMap_OLD" sheetId="70" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3304" uniqueCount="1232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3307" uniqueCount="1232">
   <si>
     <t>Unit</t>
   </si>
@@ -9094,11 +9094,11 @@
         <v>a 3 deg.kAnn</v>
       </c>
       <c r="H10" t="str">
-        <f t="shared" ref="H7:H60" si="5">_xlfn.TEXTJOIN(".",TRUE,I10:J10)</f>
+        <f t="shared" ref="H10:H60" si="5">_xlfn.TEXTJOIN(".",TRUE,I10:J10)</f>
         <v>a 3 deg.kAnn</v>
       </c>
       <c r="I10" t="str">
-        <f t="shared" ref="I7:I60" si="6">VLOOKUP(R10,$W$6:$X$12,2,FALSE)</f>
+        <f t="shared" ref="I10:I60" si="6">VLOOKUP(R10,$W$6:$X$12,2,FALSE)</f>
         <v>a 3 deg</v>
       </c>
       <c r="J10" t="str">
@@ -21110,6 +21110,9 @@
       <c r="N3" t="s">
         <v>70</v>
       </c>
+      <c r="Q3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="4" spans="1:21">
       <c r="A4" t="s">
@@ -21127,6 +21130,9 @@
       <c r="N4" t="s">
         <v>79</v>
       </c>
+      <c r="Q4" t="s">
+        <v>44</v>
+      </c>
       <c r="T4" s="8" t="s">
         <v>43</v>
       </c>
@@ -21150,6 +21156,9 @@
       </c>
       <c r="N5" t="s">
         <v>81</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>44</v>
       </c>
       <c r="T5" s="3" t="s">
         <v>44</v>

--- a/ReportDefs_vervestacks.xlsx
+++ b/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF629D7-6FA6-4F85-8743-2F2305CE80E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F8A92C-3AE3-4F05-9EE7-EA77C300E01D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3307" uniqueCount="1232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3304" uniqueCount="1232">
   <si>
     <t>Unit</t>
   </si>
@@ -21110,9 +21110,6 @@
       <c r="N3" t="s">
         <v>70</v>
       </c>
-      <c r="Q3" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="4" spans="1:21">
       <c r="A4" t="s">
@@ -21130,9 +21127,6 @@
       <c r="N4" t="s">
         <v>79</v>
       </c>
-      <c r="Q4" t="s">
-        <v>44</v>
-      </c>
       <c r="T4" s="8" t="s">
         <v>43</v>
       </c>
@@ -21156,9 +21150,6 @@
       </c>
       <c r="N5" t="s">
         <v>81</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>44</v>
       </c>
       <c r="T5" s="3" t="s">
         <v>44</v>

--- a/ReportDefs_vervestacks.xlsx
+++ b/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C584DA7D-AA94-47B1-85D2-8621BA6DD9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C694B33-0D0E-4A4D-A3D0-286C4E41723C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenMap" sheetId="56" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5136" uniqueCount="1229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5142" uniqueCount="1229">
   <si>
     <t>Unit</t>
   </si>
@@ -4314,7 +4314,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet11"/>
-  <dimension ref="B1:X75"/>
+  <dimension ref="B1:Y75"/>
   <sheetFormatPr defaultColWidth="14.73046875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.73046875" bestFit="1" customWidth="1"/>
@@ -4323,35 +4323,36 @@
     <col min="4" max="4" width="10.59765625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.53125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.19921875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.06640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.53125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="2.73046875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.33203125" customWidth="1"/>
-    <col min="23" max="23" width="2.73046875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.06640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.59765625" customWidth="1"/>
+    <col min="10" max="10" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.53125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.06640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.53125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="2.73046875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.33203125" customWidth="1"/>
+    <col min="24" max="24" width="2.73046875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.06640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:24">
-      <c r="I1" t="s">
+    <row r="1" spans="2:25">
+      <c r="J1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="2:24">
-      <c r="I2" t="s">
+    <row r="2" spans="2:25">
+      <c r="J2" t="s">
         <v>281</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="2:24">
+    <row r="4" spans="2:25">
       <c r="B4" t="s">
         <v>58</v>
       </c>
@@ -4359,7 +4360,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="2:24">
+    <row r="5" spans="2:25">
       <c r="B5" t="s">
         <v>19</v>
       </c>
@@ -4375,85 +4376,84 @@
       <c r="H5" t="s">
         <v>8</v>
       </c>
-      <c r="I5" t="str">
-        <f>"sg_"&amp;I2</f>
-        <v>sg_climate</v>
-      </c>
       <c r="J5" t="str">
         <f>"sg_"&amp;J2</f>
+        <v>sg_climate</v>
+      </c>
+      <c r="K5" t="str">
+        <f>"sg_"&amp;K2</f>
         <v>sg_timeslice</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
         <v>278</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>279</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>280</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>120</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="6" spans="2:24">
+    <row r="6" spans="2:25">
       <c r="B6" t="str">
-        <f>"vs~"&amp;TEXT(P6,"0000")</f>
+        <f>"vs~"&amp;TEXT(Q6,"0000")</f>
         <v>vs~0001</v>
       </c>
       <c r="C6" t="str">
         <f>H6</f>
-        <v>1tui.j12</v>
-      </c>
-      <c r="H6" t="str">
-        <f>O6</f>
-        <v>1tui.j12</v>
-      </c>
-      <c r="I6" t="str">
-        <f>R6</f>
+        <v>2_2.5deg</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1220</v>
+      </c>
+      <c r="J6" t="str">
+        <f>S6</f>
         <v>tui</v>
       </c>
-      <c r="J6" t="str">
-        <f>VLOOKUP(Q6,$T$6:$U$20,2,FALSE)</f>
+      <c r="K6" t="str">
+        <f>VLOOKUP(R6,$U$6:$V$20,2,FALSE)</f>
         <v>j12</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>236</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>5</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>1208</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>1</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>290</v>
       </c>
-      <c r="R6" t="s">
+      <c r="S6" t="s">
         <v>1209</v>
       </c>
-      <c r="T6" t="s">
+      <c r="U6" t="s">
         <v>230</v>
       </c>
-      <c r="U6" t="s">
+      <c r="V6" t="s">
         <v>356</v>
       </c>
-      <c r="W6" t="s">
+      <c r="X6" t="s">
         <v>267</v>
       </c>
-      <c r="X6" t="s">
+      <c r="Y6" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="7" spans="2:24">
+    <row r="7" spans="2:25">
       <c r="B7" t="str">
-        <f t="shared" ref="B7:B60" si="0">"vs~"&amp;TEXT(P7,"0000")</f>
+        <f t="shared" ref="B7:B60" si="0">"vs~"&amp;TEXT(Q7,"0000")</f>
         <v>vs~0002</v>
       </c>
       <c r="C7" t="str">
@@ -4461,153 +4461,151 @@
         <v>2kea.j12</v>
       </c>
       <c r="H7" t="str">
-        <f t="shared" ref="H7:H9" si="2">O7</f>
+        <f t="shared" ref="H7:H9" si="2">P7</f>
         <v>2kea.j12</v>
       </c>
-      <c r="I7" t="str">
-        <f t="shared" ref="I7:I9" si="3">R7</f>
+      <c r="J7" t="str">
+        <f t="shared" ref="J7:J9" si="3">S7</f>
         <v>kea</v>
       </c>
-      <c r="J7" t="str">
-        <f t="shared" ref="J7:J60" si="4">VLOOKUP(Q7,$T$6:$U$20,2,FALSE)</f>
+      <c r="K7" t="str">
+        <f t="shared" ref="K7:K60" si="4">VLOOKUP(R7,$U$6:$V$20,2,FALSE)</f>
         <v>j12</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>237</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>5</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>1210</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>2</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" t="s">
         <v>290</v>
       </c>
-      <c r="R7" t="s">
+      <c r="S7" t="s">
         <v>1211</v>
       </c>
-      <c r="T7" t="s">
+      <c r="U7" t="s">
         <v>284</v>
       </c>
-      <c r="U7" t="s">
+      <c r="V7" t="s">
         <v>357</v>
       </c>
-      <c r="W7" t="s">
+      <c r="X7" t="s">
         <v>268</v>
       </c>
-      <c r="X7" t="s">
+      <c r="Y7" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="8" spans="2:24">
+    <row r="8" spans="2:25">
       <c r="B8" t="str">
         <f t="shared" si="0"/>
         <v>vs~0003</v>
       </c>
       <c r="C8" t="str">
         <f t="shared" si="1"/>
-        <v>0bas.j12</v>
-      </c>
-      <c r="H8" t="str">
-        <f t="shared" si="2"/>
-        <v>0bas.j12</v>
-      </c>
-      <c r="I8" t="str">
+        <v>1_Ref</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1216</v>
+      </c>
+      <c r="J8" t="str">
         <f t="shared" si="3"/>
         <v>bas</v>
       </c>
-      <c r="J8" t="str">
+      <c r="K8" t="str">
         <f t="shared" si="4"/>
         <v>j12</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>238</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>5</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>1212</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>3</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
         <v>290</v>
       </c>
-      <c r="R8" t="s">
+      <c r="S8" t="s">
         <v>1213</v>
       </c>
-      <c r="T8" t="s">
+      <c r="U8" t="s">
         <v>290</v>
       </c>
-      <c r="U8" t="s">
+      <c r="V8" t="s">
         <v>358</v>
       </c>
-      <c r="W8" t="s">
+      <c r="X8" t="s">
         <v>269</v>
       </c>
-      <c r="X8" t="s">
+      <c r="Y8" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="9" spans="2:24">
+    <row r="9" spans="2:25">
       <c r="B9" t="str">
         <f t="shared" si="0"/>
         <v>vs~0004</v>
       </c>
       <c r="C9" t="str">
         <f t="shared" si="1"/>
-        <v>3nz.j12</v>
-      </c>
-      <c r="H9" t="str">
-        <f t="shared" si="2"/>
-        <v>3nz.j12</v>
-      </c>
-      <c r="I9" t="str">
+        <v>3_1.5deg</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1219</v>
+      </c>
+      <c r="J9" t="str">
         <f t="shared" si="3"/>
         <v>nz</v>
       </c>
-      <c r="J9" t="str">
+      <c r="K9" t="str">
         <f t="shared" si="4"/>
         <v>j12</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>239</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>5</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>1214</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>4</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="R9" t="s">
         <v>290</v>
       </c>
-      <c r="R9" t="s">
+      <c r="S9" t="s">
         <v>1215</v>
       </c>
-      <c r="T9" t="s">
+      <c r="U9" t="s">
         <v>296</v>
       </c>
-      <c r="U9" t="s">
+      <c r="V9" t="s">
         <v>359</v>
       </c>
-      <c r="W9" t="s">
+      <c r="X9" t="s">
         <v>270</v>
       </c>
-      <c r="X9" t="s">
+      <c r="Y9" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="10" spans="2:24">
+    <row r="10" spans="2:25">
       <c r="B10" t="str">
         <f t="shared" si="0"/>
         <v>vs~0005</v>
@@ -4617,49 +4615,49 @@
         <v>a 3 deg.kAnn</v>
       </c>
       <c r="H10" t="str">
-        <f t="shared" ref="H10:H60" si="5">_xlfn.TEXTJOIN(".",TRUE,I10:J10)</f>
+        <f t="shared" ref="H10:H60" si="5">_xlfn.TEXTJOIN(".",TRUE,J10:K10)</f>
         <v>a 3 deg.kAnn</v>
       </c>
-      <c r="I10" t="str">
-        <f t="shared" ref="I10:I60" si="6">VLOOKUP(R10,$W$6:$X$12,2,FALSE)</f>
+      <c r="J10" t="str">
+        <f t="shared" ref="J10:J60" si="6">VLOOKUP(S10,$X$6:$Y$12,2,FALSE)</f>
         <v>a 3 deg</v>
       </c>
-      <c r="J10" t="str">
+      <c r="K10" t="str">
         <f t="shared" si="4"/>
         <v>kAnn</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>240</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>5</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>282</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>5</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="R10" t="s">
         <v>230</v>
       </c>
-      <c r="R10" t="s">
+      <c r="S10" t="s">
         <v>271</v>
       </c>
-      <c r="T10" t="s">
+      <c r="U10" t="s">
         <v>302</v>
       </c>
-      <c r="U10" t="s">
+      <c r="V10" t="s">
         <v>360</v>
       </c>
-      <c r="W10" t="s">
+      <c r="X10" t="s">
         <v>271</v>
       </c>
-      <c r="X10" t="s">
+      <c r="Y10" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="11" spans="2:24">
+    <row r="11" spans="2:25">
       <c r="B11" t="str">
         <f t="shared" si="0"/>
         <v>vs~0006</v>
@@ -4672,37 +4670,37 @@
         <f t="shared" si="5"/>
         <v>e 1.5 deg no OS.k12</v>
       </c>
-      <c r="I11" t="str">
+      <c r="J11" t="str">
         <f t="shared" si="6"/>
         <v>e 1.5 deg no OS</v>
       </c>
-      <c r="J11" t="str">
+      <c r="K11" t="str">
         <f t="shared" si="4"/>
         <v>k12</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>5</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>283</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>6</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="R11" t="s">
         <v>284</v>
       </c>
-      <c r="R11" t="s">
+      <c r="S11" t="s">
         <v>267</v>
       </c>
-      <c r="T11" t="s">
+      <c r="U11" t="s">
         <v>308</v>
       </c>
-      <c r="U11" t="s">
+      <c r="V11" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="12" spans="2:24">
+    <row r="12" spans="2:25">
       <c r="B12" t="str">
         <f t="shared" si="0"/>
         <v>vs~0007</v>
@@ -4715,37 +4713,37 @@
         <f t="shared" si="5"/>
         <v>d 1.5 deg OS.k12</v>
       </c>
-      <c r="I12" t="str">
+      <c r="J12" t="str">
         <f t="shared" si="6"/>
         <v>d 1.5 deg OS</v>
       </c>
-      <c r="J12" t="str">
+      <c r="K12" t="str">
         <f t="shared" si="4"/>
         <v>k12</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>5</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>285</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>7</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="R12" t="s">
         <v>284</v>
       </c>
-      <c r="R12" t="s">
+      <c r="S12" t="s">
         <v>268</v>
       </c>
-      <c r="T12" t="s">
+      <c r="U12" t="s">
         <v>314</v>
       </c>
-      <c r="U12" t="s">
+      <c r="V12" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="13" spans="2:24">
+    <row r="13" spans="2:25">
       <c r="B13" t="str">
         <f t="shared" si="0"/>
         <v>vs~0008</v>
@@ -4758,37 +4756,37 @@
         <f t="shared" si="5"/>
         <v>c 2 deg (67%).k12</v>
       </c>
-      <c r="I13" t="str">
+      <c r="J13" t="str">
         <f t="shared" si="6"/>
         <v>c 2 deg (67%)</v>
       </c>
-      <c r="J13" t="str">
+      <c r="K13" t="str">
         <f t="shared" si="4"/>
         <v>k12</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>5</v>
       </c>
-      <c r="O13" t="s">
+      <c r="P13" t="s">
         <v>286</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>8</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="R13" t="s">
         <v>284</v>
       </c>
-      <c r="R13" t="s">
+      <c r="S13" t="s">
         <v>269</v>
       </c>
-      <c r="T13" t="s">
+      <c r="U13" t="s">
         <v>320</v>
       </c>
-      <c r="U13" t="s">
+      <c r="V13" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="14" spans="2:24">
+    <row r="14" spans="2:25">
       <c r="B14" t="str">
         <f t="shared" si="0"/>
         <v>vs~0009</v>
@@ -4801,37 +4799,37 @@
         <f t="shared" si="5"/>
         <v>b 2 deg (50%).k12</v>
       </c>
-      <c r="I14" t="str">
+      <c r="J14" t="str">
         <f t="shared" si="6"/>
         <v>b 2 deg (50%)</v>
       </c>
-      <c r="J14" t="str">
+      <c r="K14" t="str">
         <f t="shared" si="4"/>
         <v>k12</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>5</v>
       </c>
-      <c r="O14" t="s">
+      <c r="P14" t="s">
         <v>287</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>9</v>
       </c>
-      <c r="Q14" t="s">
+      <c r="R14" t="s">
         <v>284</v>
       </c>
-      <c r="R14" t="s">
+      <c r="S14" t="s">
         <v>270</v>
       </c>
-      <c r="T14" t="s">
+      <c r="U14" t="s">
         <v>326</v>
       </c>
-      <c r="U14" t="s">
+      <c r="V14" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="15" spans="2:24">
+    <row r="15" spans="2:25">
       <c r="B15" t="str">
         <f t="shared" si="0"/>
         <v>vs~0010</v>
@@ -4844,37 +4842,37 @@
         <f t="shared" si="5"/>
         <v>a 3 deg.k12</v>
       </c>
-      <c r="I15" t="str">
+      <c r="J15" t="str">
         <f t="shared" si="6"/>
         <v>a 3 deg</v>
       </c>
-      <c r="J15" t="str">
+      <c r="K15" t="str">
         <f t="shared" si="4"/>
         <v>k12</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>5</v>
       </c>
-      <c r="O15" t="s">
+      <c r="P15" t="s">
         <v>288</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>10</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="R15" t="s">
         <v>284</v>
       </c>
-      <c r="R15" t="s">
+      <c r="S15" t="s">
         <v>271</v>
       </c>
-      <c r="T15" t="s">
+      <c r="U15" t="s">
         <v>225</v>
       </c>
-      <c r="U15" t="s">
+      <c r="V15" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="16" spans="2:24">
+    <row r="16" spans="2:25">
       <c r="B16" t="str">
         <f t="shared" si="0"/>
         <v>vs~0011</v>
@@ -4887,37 +4885,40 @@
         <f t="shared" si="5"/>
         <v>e 1.5 deg no OS.j12</v>
       </c>
-      <c r="I16" t="str">
+      <c r="J16" t="str">
         <f t="shared" si="6"/>
         <v>e 1.5 deg no OS</v>
       </c>
-      <c r="J16" t="str">
+      <c r="K16" t="str">
         <f t="shared" si="4"/>
         <v>j12</v>
       </c>
-      <c r="N16">
+      <c r="M16" t="s">
+        <v>1216</v>
+      </c>
+      <c r="O16">
         <v>5</v>
       </c>
-      <c r="O16" t="s">
+      <c r="P16" t="s">
         <v>289</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>11</v>
       </c>
-      <c r="Q16" t="s">
+      <c r="R16" t="s">
         <v>290</v>
       </c>
-      <c r="R16" t="s">
+      <c r="S16" t="s">
         <v>267</v>
       </c>
-      <c r="T16" t="s">
+      <c r="U16" t="s">
         <v>226</v>
       </c>
-      <c r="U16" t="s">
+      <c r="V16" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="17" spans="2:21">
+    <row r="17" spans="2:22">
       <c r="B17" t="str">
         <f t="shared" si="0"/>
         <v>vs~0012</v>
@@ -4930,37 +4931,40 @@
         <f t="shared" si="5"/>
         <v>d 1.5 deg OS.j12</v>
       </c>
-      <c r="I17" t="str">
+      <c r="J17" t="str">
         <f t="shared" si="6"/>
         <v>d 1.5 deg OS</v>
       </c>
-      <c r="J17" t="str">
+      <c r="K17" t="str">
         <f t="shared" si="4"/>
         <v>j12</v>
       </c>
-      <c r="N17">
+      <c r="M17" t="s">
+        <v>1219</v>
+      </c>
+      <c r="O17">
         <v>5</v>
       </c>
-      <c r="O17" t="s">
+      <c r="P17" t="s">
         <v>291</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>12</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="R17" t="s">
         <v>290</v>
       </c>
-      <c r="R17" t="s">
+      <c r="S17" t="s">
         <v>268</v>
       </c>
-      <c r="T17" t="s">
+      <c r="U17" t="s">
         <v>229</v>
       </c>
-      <c r="U17" t="s">
+      <c r="V17" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="18" spans="2:21">
+    <row r="18" spans="2:22">
       <c r="B18" t="str">
         <f t="shared" si="0"/>
         <v>vs~0013</v>
@@ -4973,37 +4977,40 @@
         <f t="shared" si="5"/>
         <v>c 2 deg (67%).j12</v>
       </c>
-      <c r="I18" t="str">
+      <c r="J18" t="str">
         <f t="shared" si="6"/>
         <v>c 2 deg (67%)</v>
       </c>
-      <c r="J18" t="str">
+      <c r="K18" t="str">
         <f t="shared" si="4"/>
         <v>j12</v>
       </c>
-      <c r="N18">
+      <c r="M18" t="s">
+        <v>1220</v>
+      </c>
+      <c r="O18">
         <v>5</v>
       </c>
-      <c r="O18" t="s">
+      <c r="P18" t="s">
         <v>292</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>13</v>
       </c>
-      <c r="Q18" t="s">
+      <c r="R18" t="s">
         <v>290</v>
       </c>
-      <c r="R18" t="s">
+      <c r="S18" t="s">
         <v>269</v>
       </c>
-      <c r="T18" t="s">
+      <c r="U18" t="s">
         <v>227</v>
       </c>
-      <c r="U18" t="s">
+      <c r="V18" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="19" spans="2:21">
+    <row r="19" spans="2:22">
       <c r="B19" t="str">
         <f t="shared" si="0"/>
         <v>vs~0014</v>
@@ -5016,37 +5023,37 @@
         <f t="shared" si="5"/>
         <v>b 2 deg (50%).j12</v>
       </c>
-      <c r="I19" t="str">
+      <c r="J19" t="str">
         <f t="shared" si="6"/>
         <v>b 2 deg (50%)</v>
       </c>
-      <c r="J19" t="str">
+      <c r="K19" t="str">
         <f t="shared" si="4"/>
         <v>j12</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>5</v>
       </c>
-      <c r="O19" t="s">
+      <c r="P19" t="s">
         <v>293</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>14</v>
       </c>
-      <c r="Q19" t="s">
+      <c r="R19" t="s">
         <v>290</v>
       </c>
-      <c r="R19" t="s">
+      <c r="S19" t="s">
         <v>270</v>
       </c>
-      <c r="T19" t="s">
+      <c r="U19" t="s">
         <v>228</v>
       </c>
-      <c r="U19" t="s">
+      <c r="V19" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="20" spans="2:21">
+    <row r="20" spans="2:22">
       <c r="B20" t="str">
         <f t="shared" si="0"/>
         <v>vs~0015</v>
@@ -5059,31 +5066,31 @@
         <f t="shared" si="5"/>
         <v>a 3 deg.j12</v>
       </c>
-      <c r="I20" t="str">
+      <c r="J20" t="str">
         <f t="shared" si="6"/>
         <v>a 3 deg</v>
       </c>
-      <c r="J20" t="str">
+      <c r="K20" t="str">
         <f t="shared" si="4"/>
         <v>j12</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>5</v>
       </c>
-      <c r="O20" t="s">
+      <c r="P20" t="s">
         <v>294</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>15</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="R20" t="s">
         <v>290</v>
       </c>
-      <c r="R20" t="s">
+      <c r="S20" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="21" spans="2:21">
+    <row r="21" spans="2:22">
       <c r="B21" t="str">
         <f t="shared" si="0"/>
         <v>vs~0016</v>
@@ -5096,31 +5103,31 @@
         <f t="shared" si="5"/>
         <v>e 1.5 deg no OS.i24</v>
       </c>
-      <c r="I21" t="str">
+      <c r="J21" t="str">
         <f t="shared" si="6"/>
         <v>e 1.5 deg no OS</v>
       </c>
-      <c r="J21" t="str">
+      <c r="K21" t="str">
         <f t="shared" si="4"/>
         <v>i24</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>5</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
         <v>295</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>16</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="R21" t="s">
         <v>296</v>
       </c>
-      <c r="R21" t="s">
+      <c r="S21" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="22" spans="2:21">
+    <row r="22" spans="2:22">
       <c r="B22" t="str">
         <f t="shared" si="0"/>
         <v>vs~0017</v>
@@ -5133,31 +5140,31 @@
         <f t="shared" si="5"/>
         <v>d 1.5 deg OS.i24</v>
       </c>
-      <c r="I22" t="str">
+      <c r="J22" t="str">
         <f t="shared" si="6"/>
         <v>d 1.5 deg OS</v>
       </c>
-      <c r="J22" t="str">
+      <c r="K22" t="str">
         <f t="shared" si="4"/>
         <v>i24</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>5</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>297</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>17</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="R22" t="s">
         <v>296</v>
       </c>
-      <c r="R22" t="s">
+      <c r="S22" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="23" spans="2:21">
+    <row r="23" spans="2:22">
       <c r="B23" t="str">
         <f t="shared" si="0"/>
         <v>vs~0018</v>
@@ -5170,31 +5177,31 @@
         <f t="shared" si="5"/>
         <v>c 2 deg (67%).i24</v>
       </c>
-      <c r="I23" t="str">
+      <c r="J23" t="str">
         <f t="shared" si="6"/>
         <v>c 2 deg (67%)</v>
       </c>
-      <c r="J23" t="str">
+      <c r="K23" t="str">
         <f t="shared" si="4"/>
         <v>i24</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>5</v>
       </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
         <v>298</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>18</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="R23" t="s">
         <v>296</v>
       </c>
-      <c r="R23" t="s">
+      <c r="S23" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="24" spans="2:21">
+    <row r="24" spans="2:22">
       <c r="B24" t="str">
         <f t="shared" si="0"/>
         <v>vs~0019</v>
@@ -5207,31 +5214,31 @@
         <f t="shared" si="5"/>
         <v>b 2 deg (50%).i24</v>
       </c>
-      <c r="I24" t="str">
+      <c r="J24" t="str">
         <f t="shared" si="6"/>
         <v>b 2 deg (50%)</v>
       </c>
-      <c r="J24" t="str">
+      <c r="K24" t="str">
         <f t="shared" si="4"/>
         <v>i24</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>5</v>
       </c>
-      <c r="O24" t="s">
+      <c r="P24" t="s">
         <v>299</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
         <v>19</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="R24" t="s">
         <v>296</v>
       </c>
-      <c r="R24" t="s">
+      <c r="S24" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="25" spans="2:21">
+    <row r="25" spans="2:22">
       <c r="B25" t="str">
         <f t="shared" si="0"/>
         <v>vs~0020</v>
@@ -5244,31 +5251,31 @@
         <f t="shared" si="5"/>
         <v>a 3 deg.i24</v>
       </c>
-      <c r="I25" t="str">
+      <c r="J25" t="str">
         <f t="shared" si="6"/>
         <v>a 3 deg</v>
       </c>
-      <c r="J25" t="str">
+      <c r="K25" t="str">
         <f t="shared" si="4"/>
         <v>i24</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <v>5</v>
       </c>
-      <c r="O25" t="s">
+      <c r="P25" t="s">
         <v>300</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
         <v>20</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="R25" t="s">
         <v>296</v>
       </c>
-      <c r="R25" t="s">
+      <c r="S25" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="26" spans="2:21">
+    <row r="26" spans="2:22">
       <c r="B26" t="str">
         <f t="shared" si="0"/>
         <v>vs~0021</v>
@@ -5281,31 +5288,31 @@
         <f t="shared" si="5"/>
         <v>e 1.5 deg no OS.h48</v>
       </c>
-      <c r="I26" t="str">
+      <c r="J26" t="str">
         <f t="shared" si="6"/>
         <v>e 1.5 deg no OS</v>
       </c>
-      <c r="J26" t="str">
+      <c r="K26" t="str">
         <f t="shared" si="4"/>
         <v>h48</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>5</v>
       </c>
-      <c r="O26" t="s">
+      <c r="P26" t="s">
         <v>301</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <v>21</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="R26" t="s">
         <v>302</v>
       </c>
-      <c r="R26" t="s">
+      <c r="S26" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="27" spans="2:21">
+    <row r="27" spans="2:22">
       <c r="B27" t="str">
         <f t="shared" si="0"/>
         <v>vs~0022</v>
@@ -5318,31 +5325,31 @@
         <f t="shared" si="5"/>
         <v>d 1.5 deg OS.h48</v>
       </c>
-      <c r="I27" t="str">
+      <c r="J27" t="str">
         <f t="shared" si="6"/>
         <v>d 1.5 deg OS</v>
       </c>
-      <c r="J27" t="str">
+      <c r="K27" t="str">
         <f t="shared" si="4"/>
         <v>h48</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>5</v>
       </c>
-      <c r="O27" t="s">
+      <c r="P27" t="s">
         <v>303</v>
       </c>
-      <c r="P27">
+      <c r="Q27">
         <v>22</v>
       </c>
-      <c r="Q27" t="s">
+      <c r="R27" t="s">
         <v>302</v>
       </c>
-      <c r="R27" t="s">
+      <c r="S27" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="28" spans="2:21">
+    <row r="28" spans="2:22">
       <c r="B28" t="str">
         <f t="shared" si="0"/>
         <v>vs~0023</v>
@@ -5355,31 +5362,31 @@
         <f t="shared" si="5"/>
         <v>c 2 deg (67%).h48</v>
       </c>
-      <c r="I28" t="str">
+      <c r="J28" t="str">
         <f t="shared" si="6"/>
         <v>c 2 deg (67%)</v>
       </c>
-      <c r="J28" t="str">
+      <c r="K28" t="str">
         <f t="shared" si="4"/>
         <v>h48</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>5</v>
       </c>
-      <c r="O28" t="s">
+      <c r="P28" t="s">
         <v>304</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <v>23</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="R28" t="s">
         <v>302</v>
       </c>
-      <c r="R28" t="s">
+      <c r="S28" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="29" spans="2:21">
+    <row r="29" spans="2:22">
       <c r="B29" t="str">
         <f t="shared" si="0"/>
         <v>vs~0024</v>
@@ -5392,31 +5399,31 @@
         <f t="shared" si="5"/>
         <v>b 2 deg (50%).h48</v>
       </c>
-      <c r="I29" t="str">
+      <c r="J29" t="str">
         <f t="shared" si="6"/>
         <v>b 2 deg (50%)</v>
       </c>
-      <c r="J29" t="str">
+      <c r="K29" t="str">
         <f t="shared" si="4"/>
         <v>h48</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>5</v>
       </c>
-      <c r="O29" t="s">
+      <c r="P29" t="s">
         <v>305</v>
       </c>
-      <c r="P29">
+      <c r="Q29">
         <v>24</v>
       </c>
-      <c r="Q29" t="s">
+      <c r="R29" t="s">
         <v>302</v>
       </c>
-      <c r="R29" t="s">
+      <c r="S29" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="30" spans="2:21">
+    <row r="30" spans="2:22">
       <c r="B30" t="str">
         <f t="shared" si="0"/>
         <v>vs~0025</v>
@@ -5429,31 +5436,31 @@
         <f t="shared" si="5"/>
         <v>a 3 deg.h48</v>
       </c>
-      <c r="I30" t="str">
+      <c r="J30" t="str">
         <f t="shared" si="6"/>
         <v>a 3 deg</v>
       </c>
-      <c r="J30" t="str">
+      <c r="K30" t="str">
         <f t="shared" si="4"/>
         <v>h48</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>5</v>
       </c>
-      <c r="O30" t="s">
+      <c r="P30" t="s">
         <v>306</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>25</v>
       </c>
-      <c r="Q30" t="s">
+      <c r="R30" t="s">
         <v>302</v>
       </c>
-      <c r="R30" t="s">
+      <c r="S30" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="31" spans="2:21">
+    <row r="31" spans="2:22">
       <c r="B31" t="str">
         <f t="shared" si="0"/>
         <v>vs~0026</v>
@@ -5466,31 +5473,31 @@
         <f t="shared" si="5"/>
         <v>e 1.5 deg no OS.g64</v>
       </c>
-      <c r="I31" t="str">
+      <c r="J31" t="str">
         <f t="shared" si="6"/>
         <v>e 1.5 deg no OS</v>
       </c>
-      <c r="J31" t="str">
+      <c r="K31" t="str">
         <f t="shared" si="4"/>
         <v>g64</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>5</v>
       </c>
-      <c r="O31" t="s">
+      <c r="P31" t="s">
         <v>307</v>
       </c>
-      <c r="P31">
+      <c r="Q31">
         <v>26</v>
       </c>
-      <c r="Q31" t="s">
+      <c r="R31" t="s">
         <v>308</v>
       </c>
-      <c r="R31" t="s">
+      <c r="S31" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="32" spans="2:21">
+    <row r="32" spans="2:22">
       <c r="B32" t="str">
         <f t="shared" si="0"/>
         <v>vs~0027</v>
@@ -5503,31 +5510,31 @@
         <f t="shared" si="5"/>
         <v>d 1.5 deg OS.g64</v>
       </c>
-      <c r="I32" t="str">
+      <c r="J32" t="str">
         <f t="shared" si="6"/>
         <v>d 1.5 deg OS</v>
       </c>
-      <c r="J32" t="str">
+      <c r="K32" t="str">
         <f t="shared" si="4"/>
         <v>g64</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>5</v>
       </c>
-      <c r="O32" t="s">
+      <c r="P32" t="s">
         <v>309</v>
       </c>
-      <c r="P32">
+      <c r="Q32">
         <v>27</v>
       </c>
-      <c r="Q32" t="s">
+      <c r="R32" t="s">
         <v>308</v>
       </c>
-      <c r="R32" t="s">
+      <c r="S32" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="33" spans="2:18">
+    <row r="33" spans="2:19">
       <c r="B33" t="str">
         <f t="shared" si="0"/>
         <v>vs~0028</v>
@@ -5540,31 +5547,31 @@
         <f t="shared" si="5"/>
         <v>c 2 deg (67%).g64</v>
       </c>
-      <c r="I33" t="str">
+      <c r="J33" t="str">
         <f t="shared" si="6"/>
         <v>c 2 deg (67%)</v>
       </c>
-      <c r="J33" t="str">
+      <c r="K33" t="str">
         <f t="shared" si="4"/>
         <v>g64</v>
       </c>
-      <c r="N33">
+      <c r="O33">
         <v>5</v>
       </c>
-      <c r="O33" t="s">
+      <c r="P33" t="s">
         <v>310</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
         <v>28</v>
       </c>
-      <c r="Q33" t="s">
+      <c r="R33" t="s">
         <v>308</v>
       </c>
-      <c r="R33" t="s">
+      <c r="S33" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="34" spans="2:18">
+    <row r="34" spans="2:19">
       <c r="B34" t="str">
         <f t="shared" si="0"/>
         <v>vs~0029</v>
@@ -5577,31 +5584,31 @@
         <f t="shared" si="5"/>
         <v>b 2 deg (50%).g64</v>
       </c>
-      <c r="I34" t="str">
+      <c r="J34" t="str">
         <f t="shared" si="6"/>
         <v>b 2 deg (50%)</v>
       </c>
-      <c r="J34" t="str">
+      <c r="K34" t="str">
         <f t="shared" si="4"/>
         <v>g64</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>5</v>
       </c>
-      <c r="O34" t="s">
+      <c r="P34" t="s">
         <v>311</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
         <v>29</v>
       </c>
-      <c r="Q34" t="s">
+      <c r="R34" t="s">
         <v>308</v>
       </c>
-      <c r="R34" t="s">
+      <c r="S34" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="35" spans="2:18">
+    <row r="35" spans="2:19">
       <c r="B35" t="str">
         <f t="shared" si="0"/>
         <v>vs~0030</v>
@@ -5614,31 +5621,31 @@
         <f t="shared" si="5"/>
         <v>a 3 deg.g64</v>
       </c>
-      <c r="I35" t="str">
+      <c r="J35" t="str">
         <f t="shared" si="6"/>
         <v>a 3 deg</v>
       </c>
-      <c r="J35" t="str">
+      <c r="K35" t="str">
         <f t="shared" si="4"/>
         <v>g64</v>
       </c>
-      <c r="N35">
+      <c r="O35">
         <v>5</v>
       </c>
-      <c r="O35" t="s">
+      <c r="P35" t="s">
         <v>312</v>
       </c>
-      <c r="P35">
+      <c r="Q35">
         <v>30</v>
       </c>
-      <c r="Q35" t="s">
+      <c r="R35" t="s">
         <v>308</v>
       </c>
-      <c r="R35" t="s">
+      <c r="S35" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="36" spans="2:18">
+    <row r="36" spans="2:19">
       <c r="B36" t="str">
         <f t="shared" si="0"/>
         <v>vs~0031</v>
@@ -5651,31 +5658,31 @@
         <f t="shared" si="5"/>
         <v>e 1.5 deg no OS.f96p50</v>
       </c>
-      <c r="I36" t="str">
+      <c r="J36" t="str">
         <f t="shared" si="6"/>
         <v>e 1.5 deg no OS</v>
       </c>
-      <c r="J36" t="str">
+      <c r="K36" t="str">
         <f t="shared" si="4"/>
         <v>f96p50</v>
       </c>
-      <c r="N36">
+      <c r="O36">
         <v>5</v>
       </c>
-      <c r="O36" t="s">
+      <c r="P36" t="s">
         <v>313</v>
       </c>
-      <c r="P36">
+      <c r="Q36">
         <v>31</v>
       </c>
-      <c r="Q36" t="s">
+      <c r="R36" t="s">
         <v>314</v>
       </c>
-      <c r="R36" t="s">
+      <c r="S36" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="37" spans="2:18">
+    <row r="37" spans="2:19">
       <c r="B37" t="str">
         <f t="shared" si="0"/>
         <v>vs~0032</v>
@@ -5688,31 +5695,31 @@
         <f t="shared" si="5"/>
         <v>d 1.5 deg OS.f96p50</v>
       </c>
-      <c r="I37" t="str">
+      <c r="J37" t="str">
         <f t="shared" si="6"/>
         <v>d 1.5 deg OS</v>
       </c>
-      <c r="J37" t="str">
+      <c r="K37" t="str">
         <f t="shared" si="4"/>
         <v>f96p50</v>
       </c>
-      <c r="N37">
+      <c r="O37">
         <v>5</v>
       </c>
-      <c r="O37" t="s">
+      <c r="P37" t="s">
         <v>315</v>
       </c>
-      <c r="P37">
+      <c r="Q37">
         <v>32</v>
       </c>
-      <c r="Q37" t="s">
+      <c r="R37" t="s">
         <v>314</v>
       </c>
-      <c r="R37" t="s">
+      <c r="S37" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="38" spans="2:18">
+    <row r="38" spans="2:19">
       <c r="B38" t="str">
         <f t="shared" si="0"/>
         <v>vs~0033</v>
@@ -5725,31 +5732,31 @@
         <f t="shared" si="5"/>
         <v>c 2 deg (67%).f96p50</v>
       </c>
-      <c r="I38" t="str">
+      <c r="J38" t="str">
         <f t="shared" si="6"/>
         <v>c 2 deg (67%)</v>
       </c>
-      <c r="J38" t="str">
+      <c r="K38" t="str">
         <f t="shared" si="4"/>
         <v>f96p50</v>
       </c>
-      <c r="N38">
+      <c r="O38">
         <v>5</v>
       </c>
-      <c r="O38" t="s">
+      <c r="P38" t="s">
         <v>316</v>
       </c>
-      <c r="P38">
+      <c r="Q38">
         <v>33</v>
       </c>
-      <c r="Q38" t="s">
+      <c r="R38" t="s">
         <v>314</v>
       </c>
-      <c r="R38" t="s">
+      <c r="S38" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="39" spans="2:18">
+    <row r="39" spans="2:19">
       <c r="B39" t="str">
         <f t="shared" si="0"/>
         <v>vs~0034</v>
@@ -5762,31 +5769,31 @@
         <f t="shared" si="5"/>
         <v>b 2 deg (50%).f96p50</v>
       </c>
-      <c r="I39" t="str">
+      <c r="J39" t="str">
         <f t="shared" si="6"/>
         <v>b 2 deg (50%)</v>
       </c>
-      <c r="J39" t="str">
+      <c r="K39" t="str">
         <f t="shared" si="4"/>
         <v>f96p50</v>
       </c>
-      <c r="N39">
+      <c r="O39">
         <v>5</v>
       </c>
-      <c r="O39" t="s">
+      <c r="P39" t="s">
         <v>317</v>
       </c>
-      <c r="P39">
+      <c r="Q39">
         <v>34</v>
       </c>
-      <c r="Q39" t="s">
+      <c r="R39" t="s">
         <v>314</v>
       </c>
-      <c r="R39" t="s">
+      <c r="S39" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="40" spans="2:18">
+    <row r="40" spans="2:19">
       <c r="B40" t="str">
         <f t="shared" si="0"/>
         <v>vs~0035</v>
@@ -5799,31 +5806,31 @@
         <f t="shared" si="5"/>
         <v>a 3 deg.f96p50</v>
       </c>
-      <c r="I40" t="str">
+      <c r="J40" t="str">
         <f t="shared" si="6"/>
         <v>a 3 deg</v>
       </c>
-      <c r="J40" t="str">
+      <c r="K40" t="str">
         <f t="shared" si="4"/>
         <v>f96p50</v>
       </c>
-      <c r="N40">
+      <c r="O40">
         <v>5</v>
       </c>
-      <c r="O40" t="s">
+      <c r="P40" t="s">
         <v>318</v>
       </c>
-      <c r="P40">
+      <c r="Q40">
         <v>35</v>
       </c>
-      <c r="Q40" t="s">
+      <c r="R40" t="s">
         <v>314</v>
       </c>
-      <c r="R40" t="s">
+      <c r="S40" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="41" spans="2:18">
+    <row r="41" spans="2:19">
       <c r="B41" t="str">
         <f t="shared" si="0"/>
         <v>vs~0036</v>
@@ -5836,31 +5843,31 @@
         <f t="shared" si="5"/>
         <v>e 1.5 deg no OS.f96p10</v>
       </c>
-      <c r="I41" t="str">
+      <c r="J41" t="str">
         <f t="shared" si="6"/>
         <v>e 1.5 deg no OS</v>
       </c>
-      <c r="J41" t="str">
+      <c r="K41" t="str">
         <f t="shared" si="4"/>
         <v>f96p10</v>
       </c>
-      <c r="N41">
+      <c r="O41">
         <v>5</v>
       </c>
-      <c r="O41" t="s">
+      <c r="P41" t="s">
         <v>319</v>
       </c>
-      <c r="P41">
+      <c r="Q41">
         <v>36</v>
       </c>
-      <c r="Q41" t="s">
+      <c r="R41" t="s">
         <v>320</v>
       </c>
-      <c r="R41" t="s">
+      <c r="S41" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="42" spans="2:18">
+    <row r="42" spans="2:19">
       <c r="B42" t="str">
         <f t="shared" si="0"/>
         <v>vs~0037</v>
@@ -5873,31 +5880,31 @@
         <f t="shared" si="5"/>
         <v>d 1.5 deg OS.f96p10</v>
       </c>
-      <c r="I42" t="str">
+      <c r="J42" t="str">
         <f t="shared" si="6"/>
         <v>d 1.5 deg OS</v>
       </c>
-      <c r="J42" t="str">
+      <c r="K42" t="str">
         <f t="shared" si="4"/>
         <v>f96p10</v>
       </c>
-      <c r="N42">
+      <c r="O42">
         <v>5</v>
       </c>
-      <c r="O42" t="s">
+      <c r="P42" t="s">
         <v>321</v>
       </c>
-      <c r="P42">
+      <c r="Q42">
         <v>37</v>
       </c>
-      <c r="Q42" t="s">
+      <c r="R42" t="s">
         <v>320</v>
       </c>
-      <c r="R42" t="s">
+      <c r="S42" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="43" spans="2:18">
+    <row r="43" spans="2:19">
       <c r="B43" t="str">
         <f t="shared" si="0"/>
         <v>vs~0038</v>
@@ -5910,31 +5917,31 @@
         <f t="shared" si="5"/>
         <v>c 2 deg (67%).f96p10</v>
       </c>
-      <c r="I43" t="str">
+      <c r="J43" t="str">
         <f t="shared" si="6"/>
         <v>c 2 deg (67%)</v>
       </c>
-      <c r="J43" t="str">
+      <c r="K43" t="str">
         <f t="shared" si="4"/>
         <v>f96p10</v>
       </c>
-      <c r="N43">
+      <c r="O43">
         <v>5</v>
       </c>
-      <c r="O43" t="s">
+      <c r="P43" t="s">
         <v>322</v>
       </c>
-      <c r="P43">
+      <c r="Q43">
         <v>38</v>
       </c>
-      <c r="Q43" t="s">
+      <c r="R43" t="s">
         <v>320</v>
       </c>
-      <c r="R43" t="s">
+      <c r="S43" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="44" spans="2:18">
+    <row r="44" spans="2:19">
       <c r="B44" t="str">
         <f t="shared" si="0"/>
         <v>vs~0039</v>
@@ -5947,31 +5954,31 @@
         <f t="shared" si="5"/>
         <v>b 2 deg (50%).f96p10</v>
       </c>
-      <c r="I44" t="str">
+      <c r="J44" t="str">
         <f t="shared" si="6"/>
         <v>b 2 deg (50%)</v>
       </c>
-      <c r="J44" t="str">
+      <c r="K44" t="str">
         <f t="shared" si="4"/>
         <v>f96p10</v>
       </c>
-      <c r="N44">
+      <c r="O44">
         <v>5</v>
       </c>
-      <c r="O44" t="s">
+      <c r="P44" t="s">
         <v>323</v>
       </c>
-      <c r="P44">
+      <c r="Q44">
         <v>39</v>
       </c>
-      <c r="Q44" t="s">
+      <c r="R44" t="s">
         <v>320</v>
       </c>
-      <c r="R44" t="s">
+      <c r="S44" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="45" spans="2:18">
+    <row r="45" spans="2:19">
       <c r="B45" t="str">
         <f t="shared" si="0"/>
         <v>vs~0040</v>
@@ -5984,31 +5991,31 @@
         <f t="shared" si="5"/>
         <v>a 3 deg.f96p10</v>
       </c>
-      <c r="I45" t="str">
+      <c r="J45" t="str">
         <f t="shared" si="6"/>
         <v>a 3 deg</v>
       </c>
-      <c r="J45" t="str">
+      <c r="K45" t="str">
         <f t="shared" si="4"/>
         <v>f96p10</v>
       </c>
-      <c r="N45">
+      <c r="O45">
         <v>5</v>
       </c>
-      <c r="O45" t="s">
+      <c r="P45" t="s">
         <v>324</v>
       </c>
-      <c r="P45">
+      <c r="Q45">
         <v>40</v>
       </c>
-      <c r="Q45" t="s">
+      <c r="R45" t="s">
         <v>320</v>
       </c>
-      <c r="R45" t="s">
+      <c r="S45" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="46" spans="2:18">
+    <row r="46" spans="2:19">
       <c r="B46" t="str">
         <f t="shared" si="0"/>
         <v>vs~0041</v>
@@ -6021,31 +6028,31 @@
         <f t="shared" si="5"/>
         <v>e 1.5 deg no OS.f96p90</v>
       </c>
-      <c r="I46" t="str">
+      <c r="J46" t="str">
         <f t="shared" si="6"/>
         <v>e 1.5 deg no OS</v>
       </c>
-      <c r="J46" t="str">
+      <c r="K46" t="str">
         <f t="shared" si="4"/>
         <v>f96p90</v>
       </c>
-      <c r="N46">
+      <c r="O46">
         <v>5</v>
       </c>
-      <c r="O46" t="s">
+      <c r="P46" t="s">
         <v>325</v>
       </c>
-      <c r="P46">
+      <c r="Q46">
         <v>41</v>
       </c>
-      <c r="Q46" t="s">
+      <c r="R46" t="s">
         <v>326</v>
       </c>
-      <c r="R46" t="s">
+      <c r="S46" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="47" spans="2:18">
+    <row r="47" spans="2:19">
       <c r="B47" t="str">
         <f t="shared" si="0"/>
         <v>vs~0042</v>
@@ -6058,31 +6065,31 @@
         <f t="shared" si="5"/>
         <v>d 1.5 deg OS.f96p90</v>
       </c>
-      <c r="I47" t="str">
+      <c r="J47" t="str">
         <f t="shared" si="6"/>
         <v>d 1.5 deg OS</v>
       </c>
-      <c r="J47" t="str">
+      <c r="K47" t="str">
         <f t="shared" si="4"/>
         <v>f96p90</v>
       </c>
-      <c r="N47">
+      <c r="O47">
         <v>5</v>
       </c>
-      <c r="O47" t="s">
+      <c r="P47" t="s">
         <v>327</v>
       </c>
-      <c r="P47">
+      <c r="Q47">
         <v>42</v>
       </c>
-      <c r="Q47" t="s">
+      <c r="R47" t="s">
         <v>326</v>
       </c>
-      <c r="R47" t="s">
+      <c r="S47" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="48" spans="2:18">
+    <row r="48" spans="2:19">
       <c r="B48" t="str">
         <f t="shared" si="0"/>
         <v>vs~0043</v>
@@ -6095,31 +6102,31 @@
         <f t="shared" si="5"/>
         <v>c 2 deg (67%).f96p90</v>
       </c>
-      <c r="I48" t="str">
+      <c r="J48" t="str">
         <f t="shared" si="6"/>
         <v>c 2 deg (67%)</v>
       </c>
-      <c r="J48" t="str">
+      <c r="K48" t="str">
         <f t="shared" si="4"/>
         <v>f96p90</v>
       </c>
-      <c r="N48">
+      <c r="O48">
         <v>5</v>
       </c>
-      <c r="O48" t="s">
+      <c r="P48" t="s">
         <v>328</v>
       </c>
-      <c r="P48">
+      <c r="Q48">
         <v>43</v>
       </c>
-      <c r="Q48" t="s">
+      <c r="R48" t="s">
         <v>326</v>
       </c>
-      <c r="R48" t="s">
+      <c r="S48" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="49" spans="2:18">
+    <row r="49" spans="2:19">
       <c r="B49" t="str">
         <f t="shared" si="0"/>
         <v>vs~0044</v>
@@ -6132,31 +6139,31 @@
         <f t="shared" si="5"/>
         <v>b 2 deg (50%).f96p90</v>
       </c>
-      <c r="I49" t="str">
+      <c r="J49" t="str">
         <f t="shared" si="6"/>
         <v>b 2 deg (50%)</v>
       </c>
-      <c r="J49" t="str">
+      <c r="K49" t="str">
         <f t="shared" si="4"/>
         <v>f96p90</v>
       </c>
-      <c r="N49">
+      <c r="O49">
         <v>5</v>
       </c>
-      <c r="O49" t="s">
+      <c r="P49" t="s">
         <v>329</v>
       </c>
-      <c r="P49">
+      <c r="Q49">
         <v>44</v>
       </c>
-      <c r="Q49" t="s">
+      <c r="R49" t="s">
         <v>326</v>
       </c>
-      <c r="R49" t="s">
+      <c r="S49" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="50" spans="2:18">
+    <row r="50" spans="2:19">
       <c r="B50" t="str">
         <f t="shared" si="0"/>
         <v>vs~0045</v>
@@ -6169,31 +6176,31 @@
         <f t="shared" si="5"/>
         <v>a 3 deg.f96p90</v>
       </c>
-      <c r="I50" t="str">
+      <c r="J50" t="str">
         <f t="shared" si="6"/>
         <v>a 3 deg</v>
       </c>
-      <c r="J50" t="str">
+      <c r="K50" t="str">
         <f t="shared" si="4"/>
         <v>f96p90</v>
       </c>
-      <c r="N50">
+      <c r="O50">
         <v>5</v>
       </c>
-      <c r="O50" t="s">
+      <c r="P50" t="s">
         <v>330</v>
       </c>
-      <c r="P50">
+      <c r="Q50">
         <v>45</v>
       </c>
-      <c r="Q50" t="s">
+      <c r="R50" t="s">
         <v>326</v>
       </c>
-      <c r="R50" t="s">
+      <c r="S50" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="51" spans="2:18">
+    <row r="51" spans="2:19">
       <c r="B51" t="str">
         <f t="shared" si="0"/>
         <v>vs~0046</v>
@@ -6206,31 +6213,31 @@
         <f t="shared" si="5"/>
         <v>e 1.5 deg no OS.e3d</v>
       </c>
-      <c r="I51" t="str">
+      <c r="J51" t="str">
         <f t="shared" si="6"/>
         <v>e 1.5 deg no OS</v>
       </c>
-      <c r="J51" t="str">
+      <c r="K51" t="str">
         <f t="shared" si="4"/>
         <v>e3d</v>
       </c>
-      <c r="N51">
+      <c r="O51">
         <v>5</v>
       </c>
-      <c r="O51" t="s">
+      <c r="P51" t="s">
         <v>331</v>
       </c>
-      <c r="P51">
+      <c r="Q51">
         <v>46</v>
       </c>
-      <c r="Q51" t="s">
+      <c r="R51" t="s">
         <v>225</v>
       </c>
-      <c r="R51" t="s">
+      <c r="S51" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="52" spans="2:18">
+    <row r="52" spans="2:19">
       <c r="B52" t="str">
         <f t="shared" si="0"/>
         <v>vs~0047</v>
@@ -6243,31 +6250,31 @@
         <f t="shared" si="5"/>
         <v>d 1.5 deg OS.e3d</v>
       </c>
-      <c r="I52" t="str">
+      <c r="J52" t="str">
         <f t="shared" si="6"/>
         <v>d 1.5 deg OS</v>
       </c>
-      <c r="J52" t="str">
+      <c r="K52" t="str">
         <f t="shared" si="4"/>
         <v>e3d</v>
       </c>
-      <c r="N52">
+      <c r="O52">
         <v>5</v>
       </c>
-      <c r="O52" t="s">
+      <c r="P52" t="s">
         <v>332</v>
       </c>
-      <c r="P52">
+      <c r="Q52">
         <v>47</v>
       </c>
-      <c r="Q52" t="s">
+      <c r="R52" t="s">
         <v>225</v>
       </c>
-      <c r="R52" t="s">
+      <c r="S52" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="53" spans="2:18">
+    <row r="53" spans="2:19">
       <c r="B53" t="str">
         <f t="shared" si="0"/>
         <v>vs~0048</v>
@@ -6280,31 +6287,31 @@
         <f t="shared" si="5"/>
         <v>c 2 deg (67%).e3d</v>
       </c>
-      <c r="I53" t="str">
+      <c r="J53" t="str">
         <f t="shared" si="6"/>
         <v>c 2 deg (67%)</v>
       </c>
-      <c r="J53" t="str">
+      <c r="K53" t="str">
         <f t="shared" si="4"/>
         <v>e3d</v>
       </c>
-      <c r="N53">
+      <c r="O53">
         <v>5</v>
       </c>
-      <c r="O53" t="s">
+      <c r="P53" t="s">
         <v>333</v>
       </c>
-      <c r="P53">
+      <c r="Q53">
         <v>48</v>
       </c>
-      <c r="Q53" t="s">
+      <c r="R53" t="s">
         <v>225</v>
       </c>
-      <c r="R53" t="s">
+      <c r="S53" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="54" spans="2:18">
+    <row r="54" spans="2:19">
       <c r="B54" t="str">
         <f t="shared" si="0"/>
         <v>vs~0049</v>
@@ -6317,31 +6324,31 @@
         <f t="shared" si="5"/>
         <v>b 2 deg (50%).e3d</v>
       </c>
-      <c r="I54" t="str">
+      <c r="J54" t="str">
         <f t="shared" si="6"/>
         <v>b 2 deg (50%)</v>
       </c>
-      <c r="J54" t="str">
+      <c r="K54" t="str">
         <f t="shared" si="4"/>
         <v>e3d</v>
       </c>
-      <c r="N54">
+      <c r="O54">
         <v>5</v>
       </c>
-      <c r="O54" t="s">
+      <c r="P54" t="s">
         <v>334</v>
       </c>
-      <c r="P54">
+      <c r="Q54">
         <v>49</v>
       </c>
-      <c r="Q54" t="s">
+      <c r="R54" t="s">
         <v>225</v>
       </c>
-      <c r="R54" t="s">
+      <c r="S54" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="55" spans="2:18">
+    <row r="55" spans="2:19">
       <c r="B55" t="str">
         <f t="shared" si="0"/>
         <v>vs~0050</v>
@@ -6354,31 +6361,31 @@
         <f t="shared" si="5"/>
         <v>a 3 deg.e3d</v>
       </c>
-      <c r="I55" t="str">
+      <c r="J55" t="str">
         <f t="shared" si="6"/>
         <v>a 3 deg</v>
       </c>
-      <c r="J55" t="str">
+      <c r="K55" t="str">
         <f t="shared" si="4"/>
         <v>e3d</v>
       </c>
-      <c r="N55">
+      <c r="O55">
         <v>5</v>
       </c>
-      <c r="O55" t="s">
+      <c r="P55" t="s">
         <v>335</v>
       </c>
-      <c r="P55">
+      <c r="Q55">
         <v>50</v>
       </c>
-      <c r="Q55" t="s">
+      <c r="R55" t="s">
         <v>225</v>
       </c>
-      <c r="R55" t="s">
+      <c r="S55" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="56" spans="2:18">
+    <row r="56" spans="2:19">
       <c r="B56" t="str">
         <f t="shared" si="0"/>
         <v>vs~0051</v>
@@ -6391,31 +6398,31 @@
         <f t="shared" si="5"/>
         <v>e 1.5 deg no OS.d9d</v>
       </c>
-      <c r="I56" t="str">
+      <c r="J56" t="str">
         <f t="shared" si="6"/>
         <v>e 1.5 deg no OS</v>
       </c>
-      <c r="J56" t="str">
+      <c r="K56" t="str">
         <f t="shared" si="4"/>
         <v>d9d</v>
       </c>
-      <c r="N56">
+      <c r="O56">
         <v>5</v>
       </c>
-      <c r="O56" t="s">
+      <c r="P56" t="s">
         <v>336</v>
       </c>
-      <c r="P56">
+      <c r="Q56">
         <v>51</v>
       </c>
-      <c r="Q56" t="s">
+      <c r="R56" t="s">
         <v>226</v>
       </c>
-      <c r="R56" t="s">
+      <c r="S56" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="57" spans="2:18">
+    <row r="57" spans="2:19">
       <c r="B57" t="str">
         <f t="shared" si="0"/>
         <v>vs~0052</v>
@@ -6428,31 +6435,31 @@
         <f t="shared" si="5"/>
         <v>d 1.5 deg OS.d9d</v>
       </c>
-      <c r="I57" t="str">
+      <c r="J57" t="str">
         <f t="shared" si="6"/>
         <v>d 1.5 deg OS</v>
       </c>
-      <c r="J57" t="str">
+      <c r="K57" t="str">
         <f t="shared" si="4"/>
         <v>d9d</v>
       </c>
-      <c r="N57">
+      <c r="O57">
         <v>5</v>
       </c>
-      <c r="O57" t="s">
+      <c r="P57" t="s">
         <v>337</v>
       </c>
-      <c r="P57">
+      <c r="Q57">
         <v>52</v>
       </c>
-      <c r="Q57" t="s">
+      <c r="R57" t="s">
         <v>226</v>
       </c>
-      <c r="R57" t="s">
+      <c r="S57" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="58" spans="2:18">
+    <row r="58" spans="2:19">
       <c r="B58" t="str">
         <f t="shared" si="0"/>
         <v>vs~0053</v>
@@ -6465,31 +6472,31 @@
         <f t="shared" si="5"/>
         <v>c 2 deg (67%).d9d</v>
       </c>
-      <c r="I58" t="str">
+      <c r="J58" t="str">
         <f t="shared" si="6"/>
         <v>c 2 deg (67%)</v>
       </c>
-      <c r="J58" t="str">
+      <c r="K58" t="str">
         <f t="shared" si="4"/>
         <v>d9d</v>
       </c>
-      <c r="N58">
+      <c r="O58">
         <v>5</v>
       </c>
-      <c r="O58" t="s">
+      <c r="P58" t="s">
         <v>338</v>
       </c>
-      <c r="P58">
+      <c r="Q58">
         <v>53</v>
       </c>
-      <c r="Q58" t="s">
+      <c r="R58" t="s">
         <v>226</v>
       </c>
-      <c r="R58" t="s">
+      <c r="S58" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="59" spans="2:18">
+    <row r="59" spans="2:19">
       <c r="B59" t="str">
         <f t="shared" si="0"/>
         <v>vs~0054</v>
@@ -6502,31 +6509,31 @@
         <f t="shared" si="5"/>
         <v>b 2 deg (50%).d9d</v>
       </c>
-      <c r="I59" t="str">
+      <c r="J59" t="str">
         <f t="shared" si="6"/>
         <v>b 2 deg (50%)</v>
       </c>
-      <c r="J59" t="str">
+      <c r="K59" t="str">
         <f t="shared" si="4"/>
         <v>d9d</v>
       </c>
-      <c r="N59">
+      <c r="O59">
         <v>5</v>
       </c>
-      <c r="O59" t="s">
+      <c r="P59" t="s">
         <v>339</v>
       </c>
-      <c r="P59">
+      <c r="Q59">
         <v>54</v>
       </c>
-      <c r="Q59" t="s">
+      <c r="R59" t="s">
         <v>226</v>
       </c>
-      <c r="R59" t="s">
+      <c r="S59" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="60" spans="2:18">
+    <row r="60" spans="2:19">
       <c r="B60" t="str">
         <f t="shared" si="0"/>
         <v>vs~0055</v>
@@ -6539,33 +6546,33 @@
         <f t="shared" si="5"/>
         <v>a 3 deg.d9d</v>
       </c>
-      <c r="I60" t="str">
+      <c r="J60" t="str">
         <f t="shared" si="6"/>
         <v>a 3 deg</v>
       </c>
-      <c r="J60" t="str">
+      <c r="K60" t="str">
         <f t="shared" si="4"/>
         <v>d9d</v>
       </c>
-      <c r="N60">
+      <c r="O60">
         <v>5</v>
       </c>
-      <c r="O60" t="s">
+      <c r="P60" t="s">
         <v>340</v>
       </c>
-      <c r="P60">
+      <c r="Q60">
         <v>55</v>
       </c>
-      <c r="Q60" t="s">
+      <c r="R60" t="s">
         <v>226</v>
       </c>
-      <c r="R60" t="s">
+      <c r="S60" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="61" spans="2:18">
+    <row r="61" spans="2:19">
       <c r="B61" t="str">
-        <f t="shared" ref="B61:B75" si="10">"vs~"&amp;TEXT(P61,"0000")</f>
+        <f t="shared" ref="B61:B75" si="10">"vs~"&amp;TEXT(Q61,"0000")</f>
         <v>vs~0056</v>
       </c>
       <c r="C61" t="str">
@@ -6573,34 +6580,34 @@
         <v>e 1.5 deg no OS.c15d</v>
       </c>
       <c r="H61" t="str">
-        <f t="shared" ref="H61:H75" si="12">_xlfn.TEXTJOIN(".",TRUE,I61:J61)</f>
+        <f t="shared" ref="H61:H75" si="12">_xlfn.TEXTJOIN(".",TRUE,J61:K61)</f>
         <v>e 1.5 deg no OS.c15d</v>
       </c>
-      <c r="I61" t="str">
-        <f t="shared" ref="I61:I75" si="13">VLOOKUP(R61,$W$6:$X$12,2,FALSE)</f>
+      <c r="J61" t="str">
+        <f t="shared" ref="J61:J75" si="13">VLOOKUP(S61,$X$6:$Y$12,2,FALSE)</f>
         <v>e 1.5 deg no OS</v>
       </c>
-      <c r="J61" t="str">
-        <f t="shared" ref="J61:J75" si="14">VLOOKUP(Q61,$T$6:$U$20,2,FALSE)</f>
+      <c r="K61" t="str">
+        <f t="shared" ref="K61:K75" si="14">VLOOKUP(R61,$U$6:$V$20,2,FALSE)</f>
         <v>c15d</v>
       </c>
-      <c r="N61">
+      <c r="O61">
         <v>5</v>
       </c>
-      <c r="O61" t="s">
+      <c r="P61" t="s">
         <v>341</v>
       </c>
-      <c r="P61">
+      <c r="Q61">
         <v>56</v>
       </c>
-      <c r="Q61" t="s">
+      <c r="R61" t="s">
         <v>229</v>
       </c>
-      <c r="R61" t="s">
+      <c r="S61" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="62" spans="2:18">
+    <row r="62" spans="2:19">
       <c r="B62" t="str">
         <f t="shared" si="10"/>
         <v>vs~0057</v>
@@ -6613,31 +6620,31 @@
         <f t="shared" si="12"/>
         <v>d 1.5 deg OS.c15d</v>
       </c>
-      <c r="I62" t="str">
+      <c r="J62" t="str">
         <f t="shared" si="13"/>
         <v>d 1.5 deg OS</v>
       </c>
-      <c r="J62" t="str">
+      <c r="K62" t="str">
         <f t="shared" si="14"/>
         <v>c15d</v>
       </c>
-      <c r="N62">
+      <c r="O62">
         <v>5</v>
       </c>
-      <c r="O62" t="s">
+      <c r="P62" t="s">
         <v>342</v>
       </c>
-      <c r="P62">
+      <c r="Q62">
         <v>57</v>
       </c>
-      <c r="Q62" t="s">
+      <c r="R62" t="s">
         <v>229</v>
       </c>
-      <c r="R62" t="s">
+      <c r="S62" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="63" spans="2:18">
+    <row r="63" spans="2:19">
       <c r="B63" t="str">
         <f t="shared" si="10"/>
         <v>vs~0058</v>
@@ -6650,31 +6657,31 @@
         <f t="shared" si="12"/>
         <v>c 2 deg (67%).c15d</v>
       </c>
-      <c r="I63" t="str">
+      <c r="J63" t="str">
         <f t="shared" si="13"/>
         <v>c 2 deg (67%)</v>
       </c>
-      <c r="J63" t="str">
+      <c r="K63" t="str">
         <f t="shared" si="14"/>
         <v>c15d</v>
       </c>
-      <c r="N63">
+      <c r="O63">
         <v>5</v>
       </c>
-      <c r="O63" t="s">
+      <c r="P63" t="s">
         <v>343</v>
       </c>
-      <c r="P63">
+      <c r="Q63">
         <v>58</v>
       </c>
-      <c r="Q63" t="s">
+      <c r="R63" t="s">
         <v>229</v>
       </c>
-      <c r="R63" t="s">
+      <c r="S63" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="64" spans="2:18">
+    <row r="64" spans="2:19">
       <c r="B64" t="str">
         <f t="shared" si="10"/>
         <v>vs~0059</v>
@@ -6687,31 +6694,31 @@
         <f t="shared" si="12"/>
         <v>b 2 deg (50%).c15d</v>
       </c>
-      <c r="I64" t="str">
+      <c r="J64" t="str">
         <f t="shared" si="13"/>
         <v>b 2 deg (50%)</v>
       </c>
-      <c r="J64" t="str">
+      <c r="K64" t="str">
         <f t="shared" si="14"/>
         <v>c15d</v>
       </c>
-      <c r="N64">
+      <c r="O64">
         <v>5</v>
       </c>
-      <c r="O64" t="s">
+      <c r="P64" t="s">
         <v>344</v>
       </c>
-      <c r="P64">
+      <c r="Q64">
         <v>59</v>
       </c>
-      <c r="Q64" t="s">
+      <c r="R64" t="s">
         <v>229</v>
       </c>
-      <c r="R64" t="s">
+      <c r="S64" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="65" spans="2:18">
+    <row r="65" spans="2:19">
       <c r="B65" t="str">
         <f t="shared" si="10"/>
         <v>vs~0060</v>
@@ -6724,31 +6731,31 @@
         <f t="shared" si="12"/>
         <v>a 3 deg.c15d</v>
       </c>
-      <c r="I65" t="str">
+      <c r="J65" t="str">
         <f t="shared" si="13"/>
         <v>a 3 deg</v>
       </c>
-      <c r="J65" t="str">
+      <c r="K65" t="str">
         <f t="shared" si="14"/>
         <v>c15d</v>
       </c>
-      <c r="N65">
+      <c r="O65">
         <v>5</v>
       </c>
-      <c r="O65" t="s">
+      <c r="P65" t="s">
         <v>345</v>
       </c>
-      <c r="P65">
+      <c r="Q65">
         <v>60</v>
       </c>
-      <c r="Q65" t="s">
+      <c r="R65" t="s">
         <v>229</v>
       </c>
-      <c r="R65" t="s">
+      <c r="S65" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="66" spans="2:18">
+    <row r="66" spans="2:19">
       <c r="B66" t="str">
         <f t="shared" si="10"/>
         <v>vs~0061</v>
@@ -6761,31 +6768,31 @@
         <f t="shared" si="12"/>
         <v>e 1.5 deg no OS.b2w</v>
       </c>
-      <c r="I66" t="str">
+      <c r="J66" t="str">
         <f t="shared" si="13"/>
         <v>e 1.5 deg no OS</v>
       </c>
-      <c r="J66" t="str">
+      <c r="K66" t="str">
         <f t="shared" si="14"/>
         <v>b2w</v>
       </c>
-      <c r="N66">
+      <c r="O66">
         <v>5</v>
       </c>
-      <c r="O66" t="s">
+      <c r="P66" t="s">
         <v>346</v>
       </c>
-      <c r="P66">
+      <c r="Q66">
         <v>61</v>
       </c>
-      <c r="Q66" t="s">
+      <c r="R66" t="s">
         <v>227</v>
       </c>
-      <c r="R66" t="s">
+      <c r="S66" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="67" spans="2:18">
+    <row r="67" spans="2:19">
       <c r="B67" t="str">
         <f t="shared" si="10"/>
         <v>vs~0062</v>
@@ -6798,31 +6805,31 @@
         <f t="shared" si="12"/>
         <v>d 1.5 deg OS.b2w</v>
       </c>
-      <c r="I67" t="str">
+      <c r="J67" t="str">
         <f t="shared" si="13"/>
         <v>d 1.5 deg OS</v>
       </c>
-      <c r="J67" t="str">
+      <c r="K67" t="str">
         <f t="shared" si="14"/>
         <v>b2w</v>
       </c>
-      <c r="N67">
+      <c r="O67">
         <v>5</v>
       </c>
-      <c r="O67" t="s">
+      <c r="P67" t="s">
         <v>347</v>
       </c>
-      <c r="P67">
+      <c r="Q67">
         <v>62</v>
       </c>
-      <c r="Q67" t="s">
+      <c r="R67" t="s">
         <v>227</v>
       </c>
-      <c r="R67" t="s">
+      <c r="S67" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="68" spans="2:18">
+    <row r="68" spans="2:19">
       <c r="B68" t="str">
         <f t="shared" si="10"/>
         <v>vs~0063</v>
@@ -6835,31 +6842,31 @@
         <f t="shared" si="12"/>
         <v>c 2 deg (67%).b2w</v>
       </c>
-      <c r="I68" t="str">
+      <c r="J68" t="str">
         <f t="shared" si="13"/>
         <v>c 2 deg (67%)</v>
       </c>
-      <c r="J68" t="str">
+      <c r="K68" t="str">
         <f t="shared" si="14"/>
         <v>b2w</v>
       </c>
-      <c r="N68">
+      <c r="O68">
         <v>5</v>
       </c>
-      <c r="O68" t="s">
+      <c r="P68" t="s">
         <v>348</v>
       </c>
-      <c r="P68">
+      <c r="Q68">
         <v>63</v>
       </c>
-      <c r="Q68" t="s">
+      <c r="R68" t="s">
         <v>227</v>
       </c>
-      <c r="R68" t="s">
+      <c r="S68" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="69" spans="2:18">
+    <row r="69" spans="2:19">
       <c r="B69" t="str">
         <f t="shared" si="10"/>
         <v>vs~0064</v>
@@ -6872,31 +6879,31 @@
         <f t="shared" si="12"/>
         <v>b 2 deg (50%).b2w</v>
       </c>
-      <c r="I69" t="str">
+      <c r="J69" t="str">
         <f t="shared" si="13"/>
         <v>b 2 deg (50%)</v>
       </c>
-      <c r="J69" t="str">
+      <c r="K69" t="str">
         <f t="shared" si="14"/>
         <v>b2w</v>
       </c>
-      <c r="N69">
+      <c r="O69">
         <v>5</v>
       </c>
-      <c r="O69" t="s">
+      <c r="P69" t="s">
         <v>349</v>
       </c>
-      <c r="P69">
+      <c r="Q69">
         <v>64</v>
       </c>
-      <c r="Q69" t="s">
+      <c r="R69" t="s">
         <v>227</v>
       </c>
-      <c r="R69" t="s">
+      <c r="S69" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="70" spans="2:18">
+    <row r="70" spans="2:19">
       <c r="B70" t="str">
         <f t="shared" si="10"/>
         <v>vs~0065</v>
@@ -6909,31 +6916,31 @@
         <f t="shared" si="12"/>
         <v>a 3 deg.b2w</v>
       </c>
-      <c r="I70" t="str">
+      <c r="J70" t="str">
         <f t="shared" si="13"/>
         <v>a 3 deg</v>
       </c>
-      <c r="J70" t="str">
+      <c r="K70" t="str">
         <f t="shared" si="14"/>
         <v>b2w</v>
       </c>
-      <c r="N70">
+      <c r="O70">
         <v>5</v>
       </c>
-      <c r="O70" t="s">
+      <c r="P70" t="s">
         <v>350</v>
       </c>
-      <c r="P70">
+      <c r="Q70">
         <v>65</v>
       </c>
-      <c r="Q70" t="s">
+      <c r="R70" t="s">
         <v>227</v>
       </c>
-      <c r="R70" t="s">
+      <c r="S70" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="71" spans="2:18">
+    <row r="71" spans="2:19">
       <c r="B71" t="str">
         <f t="shared" si="10"/>
         <v>vs~0066</v>
@@ -6946,31 +6953,31 @@
         <f t="shared" si="12"/>
         <v>e 1.5 deg no OS.a2w2d</v>
       </c>
-      <c r="I71" t="str">
+      <c r="J71" t="str">
         <f t="shared" si="13"/>
         <v>e 1.5 deg no OS</v>
       </c>
-      <c r="J71" t="str">
+      <c r="K71" t="str">
         <f t="shared" si="14"/>
         <v>a2w2d</v>
       </c>
-      <c r="N71">
+      <c r="O71">
         <v>5</v>
       </c>
-      <c r="O71" t="s">
+      <c r="P71" t="s">
         <v>351</v>
       </c>
-      <c r="P71">
+      <c r="Q71">
         <v>66</v>
       </c>
-      <c r="Q71" t="s">
+      <c r="R71" t="s">
         <v>228</v>
       </c>
-      <c r="R71" t="s">
+      <c r="S71" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="72" spans="2:18">
+    <row r="72" spans="2:19">
       <c r="B72" t="str">
         <f t="shared" si="10"/>
         <v>vs~0067</v>
@@ -6983,31 +6990,31 @@
         <f t="shared" si="12"/>
         <v>d 1.5 deg OS.a2w2d</v>
       </c>
-      <c r="I72" t="str">
+      <c r="J72" t="str">
         <f t="shared" si="13"/>
         <v>d 1.5 deg OS</v>
       </c>
-      <c r="J72" t="str">
+      <c r="K72" t="str">
         <f t="shared" si="14"/>
         <v>a2w2d</v>
       </c>
-      <c r="N72">
+      <c r="O72">
         <v>5</v>
       </c>
-      <c r="O72" t="s">
+      <c r="P72" t="s">
         <v>352</v>
       </c>
-      <c r="P72">
+      <c r="Q72">
         <v>67</v>
       </c>
-      <c r="Q72" t="s">
+      <c r="R72" t="s">
         <v>228</v>
       </c>
-      <c r="R72" t="s">
+      <c r="S72" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="73" spans="2:18">
+    <row r="73" spans="2:19">
       <c r="B73" t="str">
         <f t="shared" si="10"/>
         <v>vs~0068</v>
@@ -7020,31 +7027,31 @@
         <f t="shared" si="12"/>
         <v>c 2 deg (67%).a2w2d</v>
       </c>
-      <c r="I73" t="str">
+      <c r="J73" t="str">
         <f t="shared" si="13"/>
         <v>c 2 deg (67%)</v>
       </c>
-      <c r="J73" t="str">
+      <c r="K73" t="str">
         <f t="shared" si="14"/>
         <v>a2w2d</v>
       </c>
-      <c r="N73">
+      <c r="O73">
         <v>5</v>
       </c>
-      <c r="O73" t="s">
+      <c r="P73" t="s">
         <v>353</v>
       </c>
-      <c r="P73">
+      <c r="Q73">
         <v>68</v>
       </c>
-      <c r="Q73" t="s">
+      <c r="R73" t="s">
         <v>228</v>
       </c>
-      <c r="R73" t="s">
+      <c r="S73" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="74" spans="2:18">
+    <row r="74" spans="2:19">
       <c r="B74" t="str">
         <f t="shared" si="10"/>
         <v>vs~0069</v>
@@ -7057,31 +7064,31 @@
         <f t="shared" si="12"/>
         <v>b 2 deg (50%).a2w2d</v>
       </c>
-      <c r="I74" t="str">
+      <c r="J74" t="str">
         <f t="shared" si="13"/>
         <v>b 2 deg (50%)</v>
       </c>
-      <c r="J74" t="str">
+      <c r="K74" t="str">
         <f t="shared" si="14"/>
         <v>a2w2d</v>
       </c>
-      <c r="N74">
+      <c r="O74">
         <v>5</v>
       </c>
-      <c r="O74" t="s">
+      <c r="P74" t="s">
         <v>354</v>
       </c>
-      <c r="P74">
+      <c r="Q74">
         <v>69</v>
       </c>
-      <c r="Q74" t="s">
+      <c r="R74" t="s">
         <v>228</v>
       </c>
-      <c r="R74" t="s">
+      <c r="S74" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="75" spans="2:18">
+    <row r="75" spans="2:19">
       <c r="B75" t="str">
         <f t="shared" si="10"/>
         <v>vs~0070</v>
@@ -7094,27 +7101,27 @@
         <f t="shared" si="12"/>
         <v>a 3 deg.a2w2d</v>
       </c>
-      <c r="I75" t="str">
+      <c r="J75" t="str">
         <f t="shared" si="13"/>
         <v>a 3 deg</v>
       </c>
-      <c r="J75" t="str">
+      <c r="K75" t="str">
         <f t="shared" si="14"/>
         <v>a2w2d</v>
       </c>
-      <c r="N75">
+      <c r="O75">
         <v>5</v>
       </c>
-      <c r="O75" t="s">
+      <c r="P75" t="s">
         <v>355</v>
       </c>
-      <c r="P75">
+      <c r="Q75">
         <v>70</v>
       </c>
-      <c r="Q75" t="s">
+      <c r="R75" t="s">
         <v>228</v>
       </c>
-      <c r="R75" t="s">
+      <c r="S75" t="s">
         <v>271</v>
       </c>
     </row>

--- a/ReportDefs_vervestacks.xlsx
+++ b/ReportDefs_vervestacks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8017E27C-CA75-40AF-99C1-5B6D5F537934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A56087-7C50-4816-97EF-87648E534F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="4" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenMap" sheetId="56" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5143" uniqueCount="1230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5144" uniqueCount="1230">
   <si>
     <t>Unit</t>
   </si>
@@ -28404,6 +28404,9 @@
       <c r="N7" t="s">
         <v>123</v>
       </c>
+      <c r="Q7" t="s">
+        <v>39</v>
+      </c>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
     </row>

--- a/ReportDefs_vervestacks.xlsx
+++ b/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A56087-7C50-4816-97EF-87648E534F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F3A4E89-1078-4789-AAB6-5EC0DD6CB6A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenMap" sheetId="56" r:id="rId1"/>
@@ -3220,9 +3220,6 @@
     <t>s_Industry</t>
   </si>
   <si>
-    <t>Industry</t>
-  </si>
-  <si>
     <t>s_Power</t>
   </si>
   <si>
@@ -3773,6 +3770,9 @@
   </si>
   <si>
     <t>scenario</t>
+  </si>
+  <si>
+    <t>Industrial</t>
   </si>
 </sst>
 </file>
@@ -4413,7 +4413,7 @@
         <v>2_2.5deg</v>
       </c>
       <c r="H6" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="J6" t="str">
         <f>S6</f>
@@ -4430,7 +4430,7 @@
         <v>5</v>
       </c>
       <c r="P6" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="Q6">
         <v>1</v>
@@ -4439,7 +4439,7 @@
         <v>289</v>
       </c>
       <c r="S6" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="U6" t="s">
         <v>229</v>
@@ -4482,7 +4482,7 @@
         <v>5</v>
       </c>
       <c r="P7" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="Q7">
         <v>2</v>
@@ -4491,7 +4491,7 @@
         <v>289</v>
       </c>
       <c r="S7" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="U7" t="s">
         <v>283</v>
@@ -4516,7 +4516,7 @@
         <v>1_Ref</v>
       </c>
       <c r="H8" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="J8" t="str">
         <f t="shared" si="3"/>
@@ -4533,7 +4533,7 @@
         <v>5</v>
       </c>
       <c r="P8" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="Q8">
         <v>3</v>
@@ -4542,7 +4542,7 @@
         <v>289</v>
       </c>
       <c r="S8" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="U8" t="s">
         <v>289</v>
@@ -4567,7 +4567,7 @@
         <v>3_1.5deg</v>
       </c>
       <c r="H9" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="J9" t="str">
         <f t="shared" si="3"/>
@@ -4584,7 +4584,7 @@
         <v>5</v>
       </c>
       <c r="P9" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="Q9">
         <v>4</v>
@@ -4593,7 +4593,7 @@
         <v>289</v>
       </c>
       <c r="S9" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="U9" t="s">
         <v>295</v>
@@ -4897,7 +4897,7 @@
         <v>j12</v>
       </c>
       <c r="M16" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="O16">
         <v>5</v>
@@ -4943,7 +4943,7 @@
         <v>j12</v>
       </c>
       <c r="M17" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="O17">
         <v>5</v>
@@ -4989,7 +4989,7 @@
         <v>j12</v>
       </c>
       <c r="M18" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="O18">
         <v>5</v>
@@ -7961,13 +7961,13 @@
         <v>64</v>
       </c>
       <c r="B57" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C57" t="s">
         <v>83</v>
       </c>
       <c r="F57" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -7975,13 +7975,13 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C58" t="s">
         <v>1199</v>
       </c>
-      <c r="C58" t="s">
+      <c r="F58" t="s">
         <v>1200</v>
-      </c>
-      <c r="F58" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -7989,13 +7989,13 @@
         <v>64</v>
       </c>
       <c r="B59" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C59" t="s">
         <v>1202</v>
       </c>
-      <c r="C59" t="s">
-        <v>1203</v>
-      </c>
       <c r="F59" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -8003,13 +8003,13 @@
         <v>64</v>
       </c>
       <c r="B60" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C60" t="s">
         <v>1204</v>
       </c>
-      <c r="C60" t="s">
-        <v>1205</v>
-      </c>
       <c r="F60" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -8017,13 +8017,13 @@
         <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="C61" t="s">
         <v>258</v>
       </c>
       <c r="F61" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -8138,7 +8138,7 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C72" t="s">
         <v>997</v>
@@ -8149,7 +8149,7 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C73" t="s">
         <v>999</v>
@@ -8160,7 +8160,7 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C74" t="s">
         <v>1001</v>
@@ -8171,7 +8171,7 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C75" t="s">
         <v>1003</v>
@@ -8182,7 +8182,7 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C76" t="s">
         <v>1005</v>
@@ -8193,7 +8193,7 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C77" t="s">
         <v>1007</v>
@@ -8204,7 +8204,7 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C78" t="s">
         <v>1009</v>
@@ -8215,7 +8215,7 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C79" t="s">
         <v>1011</v>
@@ -8226,7 +8226,7 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C80" t="s">
         <v>1013</v>
@@ -8237,7 +8237,7 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C81" t="s">
         <v>1015</v>
@@ -8248,7 +8248,7 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C82" t="s">
         <v>1017</v>
@@ -8259,7 +8259,7 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C83" t="s">
         <v>1019</v>
@@ -8270,7 +8270,7 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C84" t="s">
         <v>1021</v>
@@ -8281,7 +8281,7 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C85" t="s">
         <v>1023</v>
@@ -8292,7 +8292,7 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C86" t="s">
         <v>1025</v>
@@ -8303,7 +8303,7 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C87" t="s">
         <v>1027</v>
@@ -8314,7 +8314,7 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C88" t="s">
         <v>1029</v>
@@ -8325,7 +8325,7 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C89" t="s">
         <v>1031</v>
@@ -8336,7 +8336,7 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C90" t="s">
         <v>1033</v>
@@ -8347,7 +8347,7 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C91" t="s">
         <v>1035</v>
@@ -8405,7 +8405,7 @@
         <v>369</v>
       </c>
       <c r="C96" t="s">
-        <v>1045</v>
+        <v>1229</v>
       </c>
       <c r="D96" t="s">
         <v>1044</v>
@@ -8419,7 +8419,7 @@
         <v>37</v>
       </c>
       <c r="D97" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -8427,10 +8427,10 @@
         <v>369</v>
       </c>
       <c r="C98" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="D98" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -8438,10 +8438,10 @@
         <v>369</v>
       </c>
       <c r="C99" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="D99" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -8449,10 +8449,10 @@
         <v>369</v>
       </c>
       <c r="C100" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="D100" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -8460,10 +8460,10 @@
         <v>369</v>
       </c>
       <c r="C101" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="D101" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -8471,10 +8471,10 @@
         <v>369</v>
       </c>
       <c r="C102" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D102" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -8482,10 +8482,10 @@
         <v>369</v>
       </c>
       <c r="C103" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="D103" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -8493,329 +8493,329 @@
         <v>369</v>
       </c>
       <c r="C104" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="D104" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C105" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="D105" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C106" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="D106" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C107" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="D107" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C108" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="D108" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C109" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="D109" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C110" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="D110" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C111" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="D111" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C112" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="D112" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C113" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="D113" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C114" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="D114" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C115" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="D115" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C116" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="D116" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C117" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="D117" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C118" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="D118" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C119" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="D119" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C120" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="D120" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C121" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="D121" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C122" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="D122" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C123" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="D123" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C124" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="D124" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C125" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="D125" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C126" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="D126" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C127" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="D127" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C128" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="D128" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C129" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="D129" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C130" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="D130" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C131" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="D131" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C132" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="D132" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C133" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="D133" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
   </sheetData>
@@ -8874,409 +8874,409 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C3" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="D3" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C4" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D4" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C5" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="D5" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C6" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="D6" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C7" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="D7" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C8" t="s">
         <v>258</v>
       </c>
       <c r="D8" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C9" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="D9" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C10" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="D10" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C11" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="D11" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C12" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="D12" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C13" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="D13" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C14" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="D14" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C15" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="D15" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C16" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D16" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C17" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="D17" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C18" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="D18" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C19" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="D19" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C20" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="D20" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C21" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="D21" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C22" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="D22" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C23" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="D23" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C24" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D24" t="s">
         <v>1162</v>
-      </c>
-      <c r="D24" t="s">
-        <v>1163</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C25" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="D25" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C26" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="D26" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C27" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="D27" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C28" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="D28" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C29" t="s">
         <v>3</v>
       </c>
       <c r="D29" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C30" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="D30" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C31" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="D31" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C32" t="s">
         <v>97</v>
       </c>
       <c r="D32" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C33" t="s">
         <v>1188</v>
       </c>
-      <c r="C33" t="s">
-        <v>1189</v>
-      </c>
       <c r="D33" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C34" t="s">
         <v>1188</v>
       </c>
-      <c r="C34" t="s">
-        <v>1189</v>
-      </c>
       <c r="D34" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C35" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D35" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C36" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="D36" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C37" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="D37" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C38" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="D38" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C39" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D39" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
   </sheetData>
@@ -9302,12 +9302,12 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="B2" t="s">
         <v>278</v>
@@ -9316,36 +9316,36 @@
         <v>800</v>
       </c>
       <c r="D2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E2" t="s">
         <v>1222</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>1223</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>1224</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>1225</v>
       </c>
-      <c r="H2" t="s">
-        <v>1226</v>
-      </c>
       <c r="I2" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B3" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D3" t="s">
         <v>1215</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D3" t="s">
-        <v>1216</v>
       </c>
       <c r="E3" t="s">
         <v>123</v>
@@ -9366,16 +9366,16 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B4" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C4" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D4" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E4" t="s">
         <v>123</v>
@@ -9396,16 +9396,16 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B5" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C5" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D5" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E5" t="s">
         <v>123</v>
@@ -9426,16 +9426,16 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B6" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C6" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D6" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E6" t="s">
         <v>123</v>
@@ -9456,16 +9456,16 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B7" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D7" t="s">
         <v>1215</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1216</v>
       </c>
       <c r="E7" t="s">
         <v>123</v>
@@ -9486,16 +9486,16 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B8" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C8" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D8" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E8" t="s">
         <v>123</v>
@@ -9516,16 +9516,16 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B9" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C9" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D9" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E9" t="s">
         <v>123</v>
@@ -9546,16 +9546,16 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B10" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C10" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D10" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E10" t="s">
         <v>123</v>
@@ -9576,16 +9576,16 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B11" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D11" t="s">
         <v>1215</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1216</v>
       </c>
       <c r="E11" t="s">
         <v>123</v>
@@ -9606,16 +9606,16 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B12" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C12" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D12" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E12" t="s">
         <v>123</v>
@@ -9636,16 +9636,16 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B13" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C13" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D13" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E13" t="s">
         <v>123</v>
@@ -9666,16 +9666,16 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B14" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C14" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D14" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E14" t="s">
         <v>123</v>
@@ -9696,16 +9696,16 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B15" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D15" t="s">
         <v>1215</v>
-      </c>
-      <c r="C15" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1216</v>
       </c>
       <c r="E15" t="s">
         <v>123</v>
@@ -9726,16 +9726,16 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B16" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C16" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D16" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E16" t="s">
         <v>123</v>
@@ -9756,16 +9756,16 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B17" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C17" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D17" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E17" t="s">
         <v>123</v>
@@ -9786,16 +9786,16 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B18" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C18" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D18" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E18" t="s">
         <v>123</v>
@@ -9816,16 +9816,16 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B19" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D19" t="s">
         <v>1215</v>
-      </c>
-      <c r="C19" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D19" t="s">
-        <v>1216</v>
       </c>
       <c r="E19" t="s">
         <v>123</v>
@@ -9846,16 +9846,16 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B20" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C20" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D20" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E20" t="s">
         <v>123</v>
@@ -9876,16 +9876,16 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B21" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C21" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D21" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E21" t="s">
         <v>123</v>
@@ -9906,16 +9906,16 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B22" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C22" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D22" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E22" t="s">
         <v>123</v>
@@ -9936,16 +9936,16 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B23" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D23" t="s">
         <v>1215</v>
-      </c>
-      <c r="C23" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D23" t="s">
-        <v>1216</v>
       </c>
       <c r="E23" t="s">
         <v>123</v>
@@ -9966,16 +9966,16 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B24" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C24" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D24" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E24" t="s">
         <v>123</v>
@@ -9996,16 +9996,16 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B25" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C25" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D25" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E25" t="s">
         <v>123</v>
@@ -10026,16 +10026,16 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B26" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C26" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D26" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E26" t="s">
         <v>123</v>
@@ -10056,16 +10056,16 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B27" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D27" t="s">
         <v>1215</v>
-      </c>
-      <c r="C27" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D27" t="s">
-        <v>1216</v>
       </c>
       <c r="E27" t="s">
         <v>123</v>
@@ -10086,16 +10086,16 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B28" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C28" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D28" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E28" t="s">
         <v>123</v>
@@ -10116,16 +10116,16 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B29" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C29" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D29" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E29" t="s">
         <v>123</v>
@@ -10146,16 +10146,16 @@
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B30" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C30" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D30" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E30" t="s">
         <v>123</v>
@@ -10176,16 +10176,16 @@
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B31" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D31" t="s">
         <v>1215</v>
-      </c>
-      <c r="C31" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D31" t="s">
-        <v>1216</v>
       </c>
       <c r="E31" t="s">
         <v>123</v>
@@ -10206,16 +10206,16 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B32" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C32" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D32" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E32" t="s">
         <v>123</v>
@@ -10236,16 +10236,16 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B33" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C33" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D33" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E33" t="s">
         <v>123</v>
@@ -10266,16 +10266,16 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B34" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C34" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D34" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E34" t="s">
         <v>123</v>
@@ -10296,16 +10296,16 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B35" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D35" t="s">
         <v>1215</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D35" t="s">
-        <v>1216</v>
       </c>
       <c r="E35" t="s">
         <v>123</v>
@@ -10326,16 +10326,16 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B36" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C36" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D36" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E36" t="s">
         <v>123</v>
@@ -10356,16 +10356,16 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B37" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C37" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D37" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E37" t="s">
         <v>123</v>
@@ -10386,16 +10386,16 @@
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B38" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C38" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D38" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E38" t="s">
         <v>123</v>
@@ -10416,16 +10416,16 @@
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B39" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D39" t="s">
         <v>1215</v>
-      </c>
-      <c r="C39" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D39" t="s">
-        <v>1216</v>
       </c>
       <c r="E39" t="s">
         <v>123</v>
@@ -10446,16 +10446,16 @@
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B40" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C40" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D40" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E40" t="s">
         <v>123</v>
@@ -10476,16 +10476,16 @@
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B41" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C41" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D41" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E41" t="s">
         <v>123</v>
@@ -10506,16 +10506,16 @@
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B42" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C42" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D42" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E42" t="s">
         <v>123</v>
@@ -10536,16 +10536,16 @@
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B43" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D43" t="s">
         <v>1215</v>
-      </c>
-      <c r="C43" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D43" t="s">
-        <v>1216</v>
       </c>
       <c r="E43" t="s">
         <v>123</v>
@@ -10566,16 +10566,16 @@
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B44" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C44" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D44" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E44" t="s">
         <v>123</v>
@@ -10596,16 +10596,16 @@
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B45" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C45" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D45" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E45" t="s">
         <v>123</v>
@@ -10626,16 +10626,16 @@
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B46" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C46" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D46" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E46" t="s">
         <v>123</v>
@@ -10656,16 +10656,16 @@
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B47" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D47" t="s">
         <v>1215</v>
-      </c>
-      <c r="C47" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D47" t="s">
-        <v>1216</v>
       </c>
       <c r="E47" t="s">
         <v>123</v>
@@ -10686,16 +10686,16 @@
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B48" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C48" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D48" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E48" t="s">
         <v>123</v>
@@ -10716,16 +10716,16 @@
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B49" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C49" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D49" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E49" t="s">
         <v>123</v>
@@ -10746,16 +10746,16 @@
     </row>
     <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B50" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C50" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D50" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E50" t="s">
         <v>123</v>
@@ -10776,16 +10776,16 @@
     </row>
     <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B51" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D51" t="s">
         <v>1215</v>
-      </c>
-      <c r="C51" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D51" t="s">
-        <v>1216</v>
       </c>
       <c r="E51" t="s">
         <v>123</v>
@@ -10806,16 +10806,16 @@
     </row>
     <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B52" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C52" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D52" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E52" t="s">
         <v>123</v>
@@ -10836,16 +10836,16 @@
     </row>
     <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B53" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C53" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D53" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E53" t="s">
         <v>123</v>
@@ -10866,16 +10866,16 @@
     </row>
     <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B54" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C54" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D54" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E54" t="s">
         <v>123</v>
@@ -10896,16 +10896,16 @@
     </row>
     <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B55" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D55" t="s">
         <v>1215</v>
-      </c>
-      <c r="C55" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D55" t="s">
-        <v>1216</v>
       </c>
       <c r="E55" t="s">
         <v>123</v>
@@ -10926,16 +10926,16 @@
     </row>
     <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B56" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C56" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D56" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E56" t="s">
         <v>123</v>
@@ -10956,16 +10956,16 @@
     </row>
     <row r="57" spans="1:9">
       <c r="A57" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B57" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C57" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D57" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E57" t="s">
         <v>123</v>
@@ -10986,16 +10986,16 @@
     </row>
     <row r="58" spans="1:9">
       <c r="A58" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B58" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C58" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D58" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E58" t="s">
         <v>123</v>
@@ -11016,16 +11016,16 @@
     </row>
     <row r="59" spans="1:9">
       <c r="A59" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B59" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D59" t="s">
         <v>1215</v>
-      </c>
-      <c r="C59" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D59" t="s">
-        <v>1216</v>
       </c>
       <c r="E59" t="s">
         <v>123</v>
@@ -11046,16 +11046,16 @@
     </row>
     <row r="60" spans="1:9">
       <c r="A60" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B60" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C60" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D60" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E60" t="s">
         <v>123</v>
@@ -11076,16 +11076,16 @@
     </row>
     <row r="61" spans="1:9">
       <c r="A61" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B61" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C61" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D61" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E61" t="s">
         <v>123</v>
@@ -11106,16 +11106,16 @@
     </row>
     <row r="62" spans="1:9">
       <c r="A62" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B62" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C62" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D62" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E62" t="s">
         <v>123</v>
@@ -11136,16 +11136,16 @@
     </row>
     <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B63" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D63" t="s">
         <v>1215</v>
-      </c>
-      <c r="C63" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D63" t="s">
-        <v>1216</v>
       </c>
       <c r="E63" t="s">
         <v>123</v>
@@ -11166,16 +11166,16 @@
     </row>
     <row r="64" spans="1:9">
       <c r="A64" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B64" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C64" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D64" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E64" t="s">
         <v>123</v>
@@ -11196,16 +11196,16 @@
     </row>
     <row r="65" spans="1:9">
       <c r="A65" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B65" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C65" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D65" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E65" t="s">
         <v>123</v>
@@ -11226,16 +11226,16 @@
     </row>
     <row r="66" spans="1:9">
       <c r="A66" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B66" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C66" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D66" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E66" t="s">
         <v>123</v>
@@ -11256,16 +11256,16 @@
     </row>
     <row r="67" spans="1:9">
       <c r="A67" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B67" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D67" t="s">
         <v>1215</v>
-      </c>
-      <c r="C67" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D67" t="s">
-        <v>1216</v>
       </c>
       <c r="E67" t="s">
         <v>123</v>
@@ -11286,16 +11286,16 @@
     </row>
     <row r="68" spans="1:9">
       <c r="A68" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B68" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C68" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D68" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E68" t="s">
         <v>123</v>
@@ -11316,16 +11316,16 @@
     </row>
     <row r="69" spans="1:9">
       <c r="A69" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B69" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C69" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D69" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E69" t="s">
         <v>123</v>
@@ -11346,16 +11346,16 @@
     </row>
     <row r="70" spans="1:9">
       <c r="A70" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B70" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C70" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D70" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E70" t="s">
         <v>123</v>
@@ -11376,16 +11376,16 @@
     </row>
     <row r="71" spans="1:9">
       <c r="A71" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B71" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D71" t="s">
         <v>1215</v>
-      </c>
-      <c r="C71" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D71" t="s">
-        <v>1216</v>
       </c>
       <c r="E71" t="s">
         <v>123</v>
@@ -11406,16 +11406,16 @@
     </row>
     <row r="72" spans="1:9">
       <c r="A72" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B72" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C72" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D72" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E72" t="s">
         <v>123</v>
@@ -11436,16 +11436,16 @@
     </row>
     <row r="73" spans="1:9">
       <c r="A73" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B73" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C73" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D73" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E73" t="s">
         <v>123</v>
@@ -11466,16 +11466,16 @@
     </row>
     <row r="74" spans="1:9">
       <c r="A74" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B74" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C74" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D74" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E74" t="s">
         <v>123</v>
@@ -11496,16 +11496,16 @@
     </row>
     <row r="75" spans="1:9">
       <c r="A75" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B75" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D75" t="s">
         <v>1215</v>
-      </c>
-      <c r="C75" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D75" t="s">
-        <v>1216</v>
       </c>
       <c r="E75" t="s">
         <v>123</v>
@@ -11526,16 +11526,16 @@
     </row>
     <row r="76" spans="1:9">
       <c r="A76" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B76" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C76" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D76" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E76" t="s">
         <v>123</v>
@@ -11556,16 +11556,16 @@
     </row>
     <row r="77" spans="1:9">
       <c r="A77" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B77" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C77" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D77" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E77" t="s">
         <v>123</v>
@@ -11586,16 +11586,16 @@
     </row>
     <row r="78" spans="1:9">
       <c r="A78" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B78" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C78" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D78" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E78" t="s">
         <v>123</v>
@@ -11616,16 +11616,16 @@
     </row>
     <row r="79" spans="1:9">
       <c r="A79" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B79" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D79" t="s">
         <v>1215</v>
-      </c>
-      <c r="C79" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D79" t="s">
-        <v>1216</v>
       </c>
       <c r="E79" t="s">
         <v>123</v>
@@ -11646,16 +11646,16 @@
     </row>
     <row r="80" spans="1:9">
       <c r="A80" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B80" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C80" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D80" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E80" t="s">
         <v>123</v>
@@ -11676,16 +11676,16 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B81" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C81" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D81" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E81" t="s">
         <v>123</v>
@@ -11706,16 +11706,16 @@
     </row>
     <row r="82" spans="1:9">
       <c r="A82" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B82" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C82" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D82" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E82" t="s">
         <v>123</v>
@@ -11736,16 +11736,16 @@
     </row>
     <row r="83" spans="1:9">
       <c r="A83" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B83" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C83" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D83" t="s">
         <v>1215</v>
-      </c>
-      <c r="C83" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D83" t="s">
-        <v>1216</v>
       </c>
       <c r="E83" t="s">
         <v>123</v>
@@ -11766,16 +11766,16 @@
     </row>
     <row r="84" spans="1:9">
       <c r="A84" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B84" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C84" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D84" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E84" t="s">
         <v>123</v>
@@ -11796,16 +11796,16 @@
     </row>
     <row r="85" spans="1:9">
       <c r="A85" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B85" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C85" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D85" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E85" t="s">
         <v>123</v>
@@ -11826,16 +11826,16 @@
     </row>
     <row r="86" spans="1:9">
       <c r="A86" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B86" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C86" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D86" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E86" t="s">
         <v>123</v>
@@ -11856,16 +11856,16 @@
     </row>
     <row r="87" spans="1:9">
       <c r="A87" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B87" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D87" t="s">
         <v>1215</v>
-      </c>
-      <c r="C87" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D87" t="s">
-        <v>1216</v>
       </c>
       <c r="E87" t="s">
         <v>123</v>
@@ -11886,16 +11886,16 @@
     </row>
     <row r="88" spans="1:9">
       <c r="A88" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B88" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C88" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D88" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E88" t="s">
         <v>123</v>
@@ -11916,16 +11916,16 @@
     </row>
     <row r="89" spans="1:9">
       <c r="A89" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B89" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C89" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D89" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E89" t="s">
         <v>123</v>
@@ -11946,16 +11946,16 @@
     </row>
     <row r="90" spans="1:9">
       <c r="A90" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B90" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C90" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D90" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E90" t="s">
         <v>123</v>
@@ -11976,16 +11976,16 @@
     </row>
     <row r="91" spans="1:9">
       <c r="A91" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B91" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C91" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D91" t="s">
         <v>1215</v>
-      </c>
-      <c r="C91" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D91" t="s">
-        <v>1216</v>
       </c>
       <c r="E91" t="s">
         <v>123</v>
@@ -12006,16 +12006,16 @@
     </row>
     <row r="92" spans="1:9">
       <c r="A92" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B92" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C92" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D92" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E92" t="s">
         <v>123</v>
@@ -12036,16 +12036,16 @@
     </row>
     <row r="93" spans="1:9">
       <c r="A93" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B93" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C93" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D93" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E93" t="s">
         <v>123</v>
@@ -12066,16 +12066,16 @@
     </row>
     <row r="94" spans="1:9">
       <c r="A94" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B94" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C94" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D94" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E94" t="s">
         <v>123</v>
@@ -12096,16 +12096,16 @@
     </row>
     <row r="95" spans="1:9">
       <c r="A95" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B95" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D95" t="s">
         <v>1215</v>
-      </c>
-      <c r="C95" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D95" t="s">
-        <v>1216</v>
       </c>
       <c r="E95" t="s">
         <v>123</v>
@@ -12126,16 +12126,16 @@
     </row>
     <row r="96" spans="1:9">
       <c r="A96" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B96" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C96" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D96" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E96" t="s">
         <v>123</v>
@@ -12156,16 +12156,16 @@
     </row>
     <row r="97" spans="1:9">
       <c r="A97" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B97" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C97" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D97" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E97" t="s">
         <v>123</v>
@@ -12186,16 +12186,16 @@
     </row>
     <row r="98" spans="1:9">
       <c r="A98" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B98" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C98" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D98" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E98" t="s">
         <v>123</v>
@@ -12216,16 +12216,16 @@
     </row>
     <row r="99" spans="1:9">
       <c r="A99" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B99" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C99" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D99" t="s">
         <v>1215</v>
-      </c>
-      <c r="C99" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D99" t="s">
-        <v>1216</v>
       </c>
       <c r="E99" t="s">
         <v>123</v>
@@ -12246,16 +12246,16 @@
     </row>
     <row r="100" spans="1:9">
       <c r="A100" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B100" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C100" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D100" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E100" t="s">
         <v>123</v>
@@ -12276,16 +12276,16 @@
     </row>
     <row r="101" spans="1:9">
       <c r="A101" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B101" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C101" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D101" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E101" t="s">
         <v>123</v>
@@ -12306,16 +12306,16 @@
     </row>
     <row r="102" spans="1:9">
       <c r="A102" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B102" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C102" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D102" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E102" t="s">
         <v>123</v>
@@ -12336,16 +12336,16 @@
     </row>
     <row r="103" spans="1:9">
       <c r="A103" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B103" t="s">
+        <v>1214</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D103" t="s">
         <v>1215</v>
-      </c>
-      <c r="C103" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D103" t="s">
-        <v>1216</v>
       </c>
       <c r="E103" t="s">
         <v>123</v>
@@ -12366,16 +12366,16 @@
     </row>
     <row r="104" spans="1:9">
       <c r="A104" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B104" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C104" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D104" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E104" t="s">
         <v>123</v>
@@ -12396,16 +12396,16 @@
     </row>
     <row r="105" spans="1:9">
       <c r="A105" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B105" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C105" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D105" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E105" t="s">
         <v>123</v>
@@ -12426,16 +12426,16 @@
     </row>
     <row r="106" spans="1:9">
       <c r="A106" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B106" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C106" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D106" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E106" t="s">
         <v>123</v>
@@ -12456,16 +12456,16 @@
     </row>
     <row r="107" spans="1:9">
       <c r="A107" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B107" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C107" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D107" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E107" t="s">
         <v>123</v>
@@ -12486,16 +12486,16 @@
     </row>
     <row r="108" spans="1:9">
       <c r="A108" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B108" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C108" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D108" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E108" t="s">
         <v>123</v>
@@ -12516,16 +12516,16 @@
     </row>
     <row r="109" spans="1:9">
       <c r="A109" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B109" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C109" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D109" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E109" t="s">
         <v>123</v>
@@ -12546,16 +12546,16 @@
     </row>
     <row r="110" spans="1:9">
       <c r="A110" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B110" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C110" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D110" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E110" t="s">
         <v>123</v>
@@ -12576,16 +12576,16 @@
     </row>
     <row r="111" spans="1:9">
       <c r="A111" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B111" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C111" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D111" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E111" t="s">
         <v>123</v>
@@ -12606,16 +12606,16 @@
     </row>
     <row r="112" spans="1:9">
       <c r="A112" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B112" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C112" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D112" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E112" t="s">
         <v>123</v>
@@ -12636,16 +12636,16 @@
     </row>
     <row r="113" spans="1:9">
       <c r="A113" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B113" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C113" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D113" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E113" t="s">
         <v>123</v>
@@ -12666,16 +12666,16 @@
     </row>
     <row r="114" spans="1:9">
       <c r="A114" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B114" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C114" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D114" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E114" t="s">
         <v>123</v>
@@ -12696,16 +12696,16 @@
     </row>
     <row r="115" spans="1:9">
       <c r="A115" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B115" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C115" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D115" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E115" t="s">
         <v>123</v>
@@ -12726,16 +12726,16 @@
     </row>
     <row r="116" spans="1:9">
       <c r="A116" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B116" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C116" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D116" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E116" t="s">
         <v>123</v>
@@ -12756,16 +12756,16 @@
     </row>
     <row r="117" spans="1:9">
       <c r="A117" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B117" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C117" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D117" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E117" t="s">
         <v>123</v>
@@ -12786,16 +12786,16 @@
     </row>
     <row r="118" spans="1:9">
       <c r="A118" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B118" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C118" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D118" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E118" t="s">
         <v>123</v>
@@ -12816,16 +12816,16 @@
     </row>
     <row r="119" spans="1:9">
       <c r="A119" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B119" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C119" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D119" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E119" t="s">
         <v>123</v>
@@ -12846,16 +12846,16 @@
     </row>
     <row r="120" spans="1:9">
       <c r="A120" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B120" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C120" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D120" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E120" t="s">
         <v>123</v>
@@ -12876,16 +12876,16 @@
     </row>
     <row r="121" spans="1:9">
       <c r="A121" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B121" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C121" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D121" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E121" t="s">
         <v>123</v>
@@ -12906,16 +12906,16 @@
     </row>
     <row r="122" spans="1:9">
       <c r="A122" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B122" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C122" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D122" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E122" t="s">
         <v>123</v>
@@ -12936,16 +12936,16 @@
     </row>
     <row r="123" spans="1:9">
       <c r="A123" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B123" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C123" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D123" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E123" t="s">
         <v>123</v>
@@ -12966,16 +12966,16 @@
     </row>
     <row r="124" spans="1:9">
       <c r="A124" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B124" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C124" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D124" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E124" t="s">
         <v>123</v>
@@ -12996,16 +12996,16 @@
     </row>
     <row r="125" spans="1:9">
       <c r="A125" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B125" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C125" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D125" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E125" t="s">
         <v>123</v>
@@ -13026,16 +13026,16 @@
     </row>
     <row r="126" spans="1:9">
       <c r="A126" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B126" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C126" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D126" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E126" t="s">
         <v>123</v>
@@ -13056,16 +13056,16 @@
     </row>
     <row r="127" spans="1:9">
       <c r="A127" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B127" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C127" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D127" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E127" t="s">
         <v>123</v>
@@ -13086,16 +13086,16 @@
     </row>
     <row r="128" spans="1:9">
       <c r="A128" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B128" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C128" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D128" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E128" t="s">
         <v>123</v>
@@ -13116,16 +13116,16 @@
     </row>
     <row r="129" spans="1:9">
       <c r="A129" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B129" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C129" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D129" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E129" t="s">
         <v>123</v>
@@ -13146,16 +13146,16 @@
     </row>
     <row r="130" spans="1:9">
       <c r="A130" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B130" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C130" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D130" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E130" t="s">
         <v>123</v>
@@ -13176,16 +13176,16 @@
     </row>
     <row r="131" spans="1:9">
       <c r="A131" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B131" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C131" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D131" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E131" t="s">
         <v>123</v>
@@ -13206,16 +13206,16 @@
     </row>
     <row r="132" spans="1:9">
       <c r="A132" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B132" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C132" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D132" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E132" t="s">
         <v>123</v>
@@ -13236,16 +13236,16 @@
     </row>
     <row r="133" spans="1:9">
       <c r="A133" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B133" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C133" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D133" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E133" t="s">
         <v>123</v>
@@ -13266,16 +13266,16 @@
     </row>
     <row r="134" spans="1:9">
       <c r="A134" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B134" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C134" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D134" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E134" t="s">
         <v>123</v>
@@ -13296,16 +13296,16 @@
     </row>
     <row r="135" spans="1:9">
       <c r="A135" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B135" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C135" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D135" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E135" t="s">
         <v>123</v>
@@ -13326,16 +13326,16 @@
     </row>
     <row r="136" spans="1:9">
       <c r="A136" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B136" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C136" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D136" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E136" t="s">
         <v>123</v>
@@ -13356,16 +13356,16 @@
     </row>
     <row r="137" spans="1:9">
       <c r="A137" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B137" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C137" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D137" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E137" t="s">
         <v>123</v>
@@ -13386,16 +13386,16 @@
     </row>
     <row r="138" spans="1:9">
       <c r="A138" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B138" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C138" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D138" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E138" t="s">
         <v>123</v>
@@ -13416,16 +13416,16 @@
     </row>
     <row r="139" spans="1:9">
       <c r="A139" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B139" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C139" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D139" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E139" t="s">
         <v>123</v>
@@ -13446,16 +13446,16 @@
     </row>
     <row r="140" spans="1:9">
       <c r="A140" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B140" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C140" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D140" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E140" t="s">
         <v>123</v>
@@ -13476,16 +13476,16 @@
     </row>
     <row r="141" spans="1:9">
       <c r="A141" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B141" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C141" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D141" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E141" t="s">
         <v>123</v>
@@ -13506,16 +13506,16 @@
     </row>
     <row r="142" spans="1:9">
       <c r="A142" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B142" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C142" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D142" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E142" t="s">
         <v>123</v>
@@ -13536,16 +13536,16 @@
     </row>
     <row r="143" spans="1:9">
       <c r="A143" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B143" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C143" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D143" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E143" t="s">
         <v>123</v>
@@ -13566,16 +13566,16 @@
     </row>
     <row r="144" spans="1:9">
       <c r="A144" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B144" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C144" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D144" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E144" t="s">
         <v>123</v>
@@ -13596,16 +13596,16 @@
     </row>
     <row r="145" spans="1:9">
       <c r="A145" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B145" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C145" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D145" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E145" t="s">
         <v>123</v>
@@ -13626,16 +13626,16 @@
     </row>
     <row r="146" spans="1:9">
       <c r="A146" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B146" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C146" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D146" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E146" t="s">
         <v>123</v>
@@ -13656,16 +13656,16 @@
     </row>
     <row r="147" spans="1:9">
       <c r="A147" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B147" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C147" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D147" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E147" t="s">
         <v>123</v>
@@ -13686,16 +13686,16 @@
     </row>
     <row r="148" spans="1:9">
       <c r="A148" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B148" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C148" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D148" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E148" t="s">
         <v>123</v>
@@ -13716,16 +13716,16 @@
     </row>
     <row r="149" spans="1:9">
       <c r="A149" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B149" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C149" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D149" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E149" t="s">
         <v>123</v>
@@ -13746,16 +13746,16 @@
     </row>
     <row r="150" spans="1:9">
       <c r="A150" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B150" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C150" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D150" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E150" t="s">
         <v>123</v>
@@ -13776,16 +13776,16 @@
     </row>
     <row r="151" spans="1:9">
       <c r="A151" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B151" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C151" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D151" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E151" t="s">
         <v>123</v>
@@ -13806,16 +13806,16 @@
     </row>
     <row r="152" spans="1:9">
       <c r="A152" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B152" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C152" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D152" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E152" t="s">
         <v>123</v>
@@ -13836,16 +13836,16 @@
     </row>
     <row r="153" spans="1:9">
       <c r="A153" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B153" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C153" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D153" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E153" t="s">
         <v>123</v>
@@ -13866,16 +13866,16 @@
     </row>
     <row r="154" spans="1:9">
       <c r="A154" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B154" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C154" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D154" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E154" t="s">
         <v>123</v>
@@ -13896,16 +13896,16 @@
     </row>
     <row r="155" spans="1:9">
       <c r="A155" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B155" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C155" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D155" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E155" t="s">
         <v>123</v>
@@ -13926,16 +13926,16 @@
     </row>
     <row r="156" spans="1:9">
       <c r="A156" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B156" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C156" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D156" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E156" t="s">
         <v>123</v>
@@ -13956,16 +13956,16 @@
     </row>
     <row r="157" spans="1:9">
       <c r="A157" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B157" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C157" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D157" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E157" t="s">
         <v>123</v>
@@ -13986,16 +13986,16 @@
     </row>
     <row r="158" spans="1:9">
       <c r="A158" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B158" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C158" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D158" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E158" t="s">
         <v>123</v>
@@ -14016,16 +14016,16 @@
     </row>
     <row r="159" spans="1:9">
       <c r="A159" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B159" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C159" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D159" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E159" t="s">
         <v>123</v>
@@ -14046,16 +14046,16 @@
     </row>
     <row r="160" spans="1:9">
       <c r="A160" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B160" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C160" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D160" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E160" t="s">
         <v>123</v>
@@ -14076,16 +14076,16 @@
     </row>
     <row r="161" spans="1:9">
       <c r="A161" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B161" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C161" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D161" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E161" t="s">
         <v>123</v>
@@ -14106,16 +14106,16 @@
     </row>
     <row r="162" spans="1:9">
       <c r="A162" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B162" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C162" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D162" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E162" t="s">
         <v>123</v>
@@ -14136,16 +14136,16 @@
     </row>
     <row r="163" spans="1:9">
       <c r="A163" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B163" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C163" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D163" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E163" t="s">
         <v>123</v>
@@ -14166,16 +14166,16 @@
     </row>
     <row r="164" spans="1:9">
       <c r="A164" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B164" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C164" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D164" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E164" t="s">
         <v>123</v>
@@ -14196,16 +14196,16 @@
     </row>
     <row r="165" spans="1:9">
       <c r="A165" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B165" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C165" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D165" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E165" t="s">
         <v>123</v>
@@ -14226,16 +14226,16 @@
     </row>
     <row r="166" spans="1:9">
       <c r="A166" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B166" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C166" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D166" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E166" t="s">
         <v>123</v>
@@ -14256,16 +14256,16 @@
     </row>
     <row r="167" spans="1:9">
       <c r="A167" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B167" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C167" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D167" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E167" t="s">
         <v>123</v>
@@ -14286,16 +14286,16 @@
     </row>
     <row r="168" spans="1:9">
       <c r="A168" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B168" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C168" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D168" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E168" t="s">
         <v>123</v>
@@ -14316,16 +14316,16 @@
     </row>
     <row r="169" spans="1:9">
       <c r="A169" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B169" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C169" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D169" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E169" t="s">
         <v>123</v>
@@ -14346,16 +14346,16 @@
     </row>
     <row r="170" spans="1:9">
       <c r="A170" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B170" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C170" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D170" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E170" t="s">
         <v>123</v>
@@ -14376,16 +14376,16 @@
     </row>
     <row r="171" spans="1:9">
       <c r="A171" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B171" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C171" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D171" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E171" t="s">
         <v>123</v>
@@ -14406,16 +14406,16 @@
     </row>
     <row r="172" spans="1:9">
       <c r="A172" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B172" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C172" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D172" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E172" t="s">
         <v>123</v>
@@ -14436,16 +14436,16 @@
     </row>
     <row r="173" spans="1:9">
       <c r="A173" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B173" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C173" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D173" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E173" t="s">
         <v>123</v>
@@ -14466,16 +14466,16 @@
     </row>
     <row r="174" spans="1:9">
       <c r="A174" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B174" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C174" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D174" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E174" t="s">
         <v>123</v>
@@ -14496,16 +14496,16 @@
     </row>
     <row r="175" spans="1:9">
       <c r="A175" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B175" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C175" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D175" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E175" t="s">
         <v>123</v>
@@ -14526,16 +14526,16 @@
     </row>
     <row r="176" spans="1:9">
       <c r="A176" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B176" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C176" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D176" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E176" t="s">
         <v>123</v>
@@ -14556,16 +14556,16 @@
     </row>
     <row r="177" spans="1:9">
       <c r="A177" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B177" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C177" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D177" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E177" t="s">
         <v>123</v>
@@ -14586,16 +14586,16 @@
     </row>
     <row r="178" spans="1:9">
       <c r="A178" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B178" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C178" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D178" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E178" t="s">
         <v>123</v>
@@ -14616,16 +14616,16 @@
     </row>
     <row r="179" spans="1:9">
       <c r="A179" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B179" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C179" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D179" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E179" t="s">
         <v>123</v>
@@ -14646,16 +14646,16 @@
     </row>
     <row r="180" spans="1:9">
       <c r="A180" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B180" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C180" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D180" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E180" t="s">
         <v>123</v>
@@ -14676,16 +14676,16 @@
     </row>
     <row r="181" spans="1:9">
       <c r="A181" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B181" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C181" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D181" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E181" t="s">
         <v>123</v>
@@ -14706,16 +14706,16 @@
     </row>
     <row r="182" spans="1:9">
       <c r="A182" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B182" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C182" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D182" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E182" t="s">
         <v>123</v>
@@ -14736,16 +14736,16 @@
     </row>
     <row r="183" spans="1:9">
       <c r="A183" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B183" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C183" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D183" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E183" t="s">
         <v>123</v>
@@ -14766,16 +14766,16 @@
     </row>
     <row r="184" spans="1:9">
       <c r="A184" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B184" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C184" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D184" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E184" t="s">
         <v>123</v>
@@ -14796,16 +14796,16 @@
     </row>
     <row r="185" spans="1:9">
       <c r="A185" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B185" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C185" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D185" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E185" t="s">
         <v>123</v>
@@ -14826,16 +14826,16 @@
     </row>
     <row r="186" spans="1:9">
       <c r="A186" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B186" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C186" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D186" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E186" t="s">
         <v>123</v>
@@ -14856,16 +14856,16 @@
     </row>
     <row r="187" spans="1:9">
       <c r="A187" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B187" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C187" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D187" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E187" t="s">
         <v>123</v>
@@ -14886,16 +14886,16 @@
     </row>
     <row r="188" spans="1:9">
       <c r="A188" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B188" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C188" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D188" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E188" t="s">
         <v>123</v>
@@ -14916,16 +14916,16 @@
     </row>
     <row r="189" spans="1:9">
       <c r="A189" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B189" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C189" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D189" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E189" t="s">
         <v>123</v>
@@ -14946,16 +14946,16 @@
     </row>
     <row r="190" spans="1:9">
       <c r="A190" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B190" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C190" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D190" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E190" t="s">
         <v>123</v>
@@ -14976,16 +14976,16 @@
     </row>
     <row r="191" spans="1:9">
       <c r="A191" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B191" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C191" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D191" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E191" t="s">
         <v>123</v>
@@ -15006,16 +15006,16 @@
     </row>
     <row r="192" spans="1:9">
       <c r="A192" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B192" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C192" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D192" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E192" t="s">
         <v>123</v>
@@ -15036,16 +15036,16 @@
     </row>
     <row r="193" spans="1:9">
       <c r="A193" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B193" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C193" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D193" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E193" t="s">
         <v>123</v>
@@ -15066,16 +15066,16 @@
     </row>
     <row r="194" spans="1:9">
       <c r="A194" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B194" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C194" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D194" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E194" t="s">
         <v>123</v>
@@ -15096,16 +15096,16 @@
     </row>
     <row r="195" spans="1:9">
       <c r="A195" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B195" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C195" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D195" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E195" t="s">
         <v>123</v>
@@ -15126,16 +15126,16 @@
     </row>
     <row r="196" spans="1:9">
       <c r="A196" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B196" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C196" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D196" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E196" t="s">
         <v>123</v>
@@ -15156,16 +15156,16 @@
     </row>
     <row r="197" spans="1:9">
       <c r="A197" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B197" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C197" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D197" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E197" t="s">
         <v>123</v>
@@ -15186,16 +15186,16 @@
     </row>
     <row r="198" spans="1:9">
       <c r="A198" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B198" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C198" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D198" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E198" t="s">
         <v>123</v>
@@ -15216,16 +15216,16 @@
     </row>
     <row r="199" spans="1:9">
       <c r="A199" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B199" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C199" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D199" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E199" t="s">
         <v>123</v>
@@ -15246,16 +15246,16 @@
     </row>
     <row r="200" spans="1:9">
       <c r="A200" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B200" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C200" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D200" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E200" t="s">
         <v>123</v>
@@ -15276,16 +15276,16 @@
     </row>
     <row r="201" spans="1:9">
       <c r="A201" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B201" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C201" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D201" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E201" t="s">
         <v>123</v>
@@ -15306,16 +15306,16 @@
     </row>
     <row r="202" spans="1:9">
       <c r="A202" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B202" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C202" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D202" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E202" t="s">
         <v>123</v>
@@ -15336,16 +15336,16 @@
     </row>
     <row r="203" spans="1:9">
       <c r="A203" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B203" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C203" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D203" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E203" t="s">
         <v>123</v>
@@ -15366,16 +15366,16 @@
     </row>
     <row r="204" spans="1:9">
       <c r="A204" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B204" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C204" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D204" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E204" t="s">
         <v>123</v>
@@ -15396,16 +15396,16 @@
     </row>
     <row r="205" spans="1:9">
       <c r="A205" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B205" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C205" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D205" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E205" t="s">
         <v>123</v>
@@ -15426,16 +15426,16 @@
     </row>
     <row r="206" spans="1:9">
       <c r="A206" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B206" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C206" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D206" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E206" t="s">
         <v>123</v>
@@ -15456,16 +15456,16 @@
     </row>
     <row r="207" spans="1:9">
       <c r="A207" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B207" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C207" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D207" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E207" t="s">
         <v>123</v>
@@ -15486,16 +15486,16 @@
     </row>
     <row r="208" spans="1:9">
       <c r="A208" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B208" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C208" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D208" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E208" t="s">
         <v>123</v>
@@ -15516,16 +15516,16 @@
     </row>
     <row r="209" spans="1:9">
       <c r="A209" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B209" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C209" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D209" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E209" t="s">
         <v>123</v>
@@ -15546,16 +15546,16 @@
     </row>
     <row r="210" spans="1:9">
       <c r="A210" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B210" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C210" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D210" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E210" t="s">
         <v>123</v>
@@ -15576,16 +15576,16 @@
     </row>
     <row r="211" spans="1:9">
       <c r="A211" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B211" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C211" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D211" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E211" t="s">
         <v>123</v>
@@ -15606,16 +15606,16 @@
     </row>
     <row r="212" spans="1:9">
       <c r="A212" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B212" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C212" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D212" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E212" t="s">
         <v>123</v>
@@ -15636,16 +15636,16 @@
     </row>
     <row r="213" spans="1:9">
       <c r="A213" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B213" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C213" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D213" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E213" t="s">
         <v>123</v>
@@ -15666,16 +15666,16 @@
     </row>
     <row r="214" spans="1:9">
       <c r="A214" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B214" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C214" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D214" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E214" t="s">
         <v>123</v>
@@ -15696,16 +15696,16 @@
     </row>
     <row r="215" spans="1:9">
       <c r="A215" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B215" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C215" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D215" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E215" t="s">
         <v>123</v>
@@ -15726,16 +15726,16 @@
     </row>
     <row r="216" spans="1:9">
       <c r="A216" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B216" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C216" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D216" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E216" t="s">
         <v>123</v>
@@ -15756,16 +15756,16 @@
     </row>
     <row r="217" spans="1:9">
       <c r="A217" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B217" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C217" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D217" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E217" t="s">
         <v>123</v>
@@ -15786,16 +15786,16 @@
     </row>
     <row r="218" spans="1:9">
       <c r="A218" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B218" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C218" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D218" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E218" t="s">
         <v>123</v>
@@ -15816,16 +15816,16 @@
     </row>
     <row r="219" spans="1:9">
       <c r="A219" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B219" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C219" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D219" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E219" t="s">
         <v>123</v>
@@ -15846,16 +15846,16 @@
     </row>
     <row r="220" spans="1:9">
       <c r="A220" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B220" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C220" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D220" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E220" t="s">
         <v>123</v>
@@ -15876,16 +15876,16 @@
     </row>
     <row r="221" spans="1:9">
       <c r="A221" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B221" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C221" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D221" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E221" t="s">
         <v>123</v>
@@ -15906,16 +15906,16 @@
     </row>
     <row r="222" spans="1:9">
       <c r="A222" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B222" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C222" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D222" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E222" t="s">
         <v>123</v>
@@ -15936,16 +15936,16 @@
     </row>
     <row r="223" spans="1:9">
       <c r="A223" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B223" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C223" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D223" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E223" t="s">
         <v>123</v>
@@ -15966,16 +15966,16 @@
     </row>
     <row r="224" spans="1:9">
       <c r="A224" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B224" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C224" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D224" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E224" t="s">
         <v>123</v>
@@ -15996,16 +15996,16 @@
     </row>
     <row r="225" spans="1:9">
       <c r="A225" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B225" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C225" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D225" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E225" t="s">
         <v>123</v>
@@ -16026,16 +16026,16 @@
     </row>
     <row r="226" spans="1:9">
       <c r="A226" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B226" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C226" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D226" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E226" t="s">
         <v>123</v>
@@ -16056,16 +16056,16 @@
     </row>
     <row r="227" spans="1:9">
       <c r="A227" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B227" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C227" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D227" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E227" t="s">
         <v>123</v>
@@ -16086,16 +16086,16 @@
     </row>
     <row r="228" spans="1:9">
       <c r="A228" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B228" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C228" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D228" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E228" t="s">
         <v>123</v>
@@ -16116,16 +16116,16 @@
     </row>
     <row r="229" spans="1:9">
       <c r="A229" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B229" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C229" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D229" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E229" t="s">
         <v>123</v>
@@ -16146,16 +16146,16 @@
     </row>
     <row r="230" spans="1:9">
       <c r="A230" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B230" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C230" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D230" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E230" t="s">
         <v>123</v>
@@ -16176,16 +16176,16 @@
     </row>
     <row r="231" spans="1:9">
       <c r="A231" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B231" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C231" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D231" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E231" t="s">
         <v>123</v>
@@ -16206,16 +16206,16 @@
     </row>
     <row r="232" spans="1:9">
       <c r="A232" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B232" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C232" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D232" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E232" t="s">
         <v>123</v>
@@ -16236,16 +16236,16 @@
     </row>
     <row r="233" spans="1:9">
       <c r="A233" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B233" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C233" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D233" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E233" t="s">
         <v>123</v>
@@ -16266,16 +16266,16 @@
     </row>
     <row r="234" spans="1:9">
       <c r="A234" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B234" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C234" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D234" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E234" t="s">
         <v>123</v>
@@ -16296,16 +16296,16 @@
     </row>
     <row r="235" spans="1:9">
       <c r="A235" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B235" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C235" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D235" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E235" t="s">
         <v>123</v>
@@ -16326,16 +16326,16 @@
     </row>
     <row r="236" spans="1:9">
       <c r="A236" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B236" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C236" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D236" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E236" t="s">
         <v>123</v>
@@ -16356,16 +16356,16 @@
     </row>
     <row r="237" spans="1:9">
       <c r="A237" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B237" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C237" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D237" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E237" t="s">
         <v>123</v>
@@ -16386,16 +16386,16 @@
     </row>
     <row r="238" spans="1:9">
       <c r="A238" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B238" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C238" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D238" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E238" t="s">
         <v>123</v>
@@ -16416,16 +16416,16 @@
     </row>
     <row r="239" spans="1:9">
       <c r="A239" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B239" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C239" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D239" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E239" t="s">
         <v>123</v>
@@ -16446,16 +16446,16 @@
     </row>
     <row r="240" spans="1:9">
       <c r="A240" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B240" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C240" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D240" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E240" t="s">
         <v>123</v>
@@ -16476,16 +16476,16 @@
     </row>
     <row r="241" spans="1:9">
       <c r="A241" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B241" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C241" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D241" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E241" t="s">
         <v>123</v>
@@ -16506,16 +16506,16 @@
     </row>
     <row r="242" spans="1:9">
       <c r="A242" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B242" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C242" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D242" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E242" t="s">
         <v>123</v>
@@ -16536,16 +16536,16 @@
     </row>
     <row r="243" spans="1:9">
       <c r="A243" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B243" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C243" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D243" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E243" t="s">
         <v>123</v>
@@ -16566,16 +16566,16 @@
     </row>
     <row r="244" spans="1:9">
       <c r="A244" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B244" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C244" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D244" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E244" t="s">
         <v>123</v>
@@ -16596,16 +16596,16 @@
     </row>
     <row r="245" spans="1:9">
       <c r="A245" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B245" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C245" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D245" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E245" t="s">
         <v>123</v>
@@ -16626,16 +16626,16 @@
     </row>
     <row r="246" spans="1:9">
       <c r="A246" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B246" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C246" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D246" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E246" t="s">
         <v>123</v>
@@ -16656,16 +16656,16 @@
     </row>
     <row r="247" spans="1:9">
       <c r="A247" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B247" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C247" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D247" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E247" t="s">
         <v>123</v>
@@ -16686,16 +16686,16 @@
     </row>
     <row r="248" spans="1:9">
       <c r="A248" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B248" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C248" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D248" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E248" t="s">
         <v>123</v>
@@ -16716,16 +16716,16 @@
     </row>
     <row r="249" spans="1:9">
       <c r="A249" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B249" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C249" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D249" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E249" t="s">
         <v>123</v>
@@ -16746,16 +16746,16 @@
     </row>
     <row r="250" spans="1:9">
       <c r="A250" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B250" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C250" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D250" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E250" t="s">
         <v>123</v>
@@ -16776,16 +16776,16 @@
     </row>
     <row r="251" spans="1:9">
       <c r="A251" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B251" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C251" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D251" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E251" t="s">
         <v>123</v>
@@ -16806,16 +16806,16 @@
     </row>
     <row r="252" spans="1:9">
       <c r="A252" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B252" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C252" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D252" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E252" t="s">
         <v>123</v>
@@ -16836,16 +16836,16 @@
     </row>
     <row r="253" spans="1:9">
       <c r="A253" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B253" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C253" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D253" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E253" t="s">
         <v>123</v>
@@ -16866,16 +16866,16 @@
     </row>
     <row r="254" spans="1:9">
       <c r="A254" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B254" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C254" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D254" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E254" t="s">
         <v>123</v>
@@ -16896,16 +16896,16 @@
     </row>
     <row r="255" spans="1:9">
       <c r="A255" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B255" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C255" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D255" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E255" t="s">
         <v>123</v>
@@ -16926,16 +16926,16 @@
     </row>
     <row r="256" spans="1:9">
       <c r="A256" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B256" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C256" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D256" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E256" t="s">
         <v>123</v>
@@ -16956,16 +16956,16 @@
     </row>
     <row r="257" spans="1:9">
       <c r="A257" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B257" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C257" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D257" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E257" t="s">
         <v>123</v>
@@ -16986,16 +16986,16 @@
     </row>
     <row r="258" spans="1:9">
       <c r="A258" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B258" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C258" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D258" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E258" t="s">
         <v>123</v>
@@ -17016,16 +17016,16 @@
     </row>
     <row r="259" spans="1:9">
       <c r="A259" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B259" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C259" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D259" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E259" t="s">
         <v>123</v>
@@ -17046,16 +17046,16 @@
     </row>
     <row r="260" spans="1:9">
       <c r="A260" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B260" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C260" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D260" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E260" t="s">
         <v>123</v>
@@ -17076,16 +17076,16 @@
     </row>
     <row r="261" spans="1:9">
       <c r="A261" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B261" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C261" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D261" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E261" t="s">
         <v>123</v>
@@ -17106,16 +17106,16 @@
     </row>
     <row r="262" spans="1:9">
       <c r="A262" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B262" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C262" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D262" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E262" t="s">
         <v>123</v>
@@ -17136,16 +17136,16 @@
     </row>
     <row r="263" spans="1:9">
       <c r="A263" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B263" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C263" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D263" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E263" t="s">
         <v>123</v>
@@ -17166,16 +17166,16 @@
     </row>
     <row r="264" spans="1:9">
       <c r="A264" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B264" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C264" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D264" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E264" t="s">
         <v>123</v>
@@ -17196,16 +17196,16 @@
     </row>
     <row r="265" spans="1:9">
       <c r="A265" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B265" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C265" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D265" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E265" t="s">
         <v>123</v>
@@ -17226,16 +17226,16 @@
     </row>
     <row r="266" spans="1:9">
       <c r="A266" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B266" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C266" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D266" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E266" t="s">
         <v>123</v>
@@ -17256,16 +17256,16 @@
     </row>
     <row r="267" spans="1:9">
       <c r="A267" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B267" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C267" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D267" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E267" t="s">
         <v>123</v>
@@ -17286,16 +17286,16 @@
     </row>
     <row r="268" spans="1:9">
       <c r="A268" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B268" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C268" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D268" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E268" t="s">
         <v>123</v>
@@ -17316,16 +17316,16 @@
     </row>
     <row r="269" spans="1:9">
       <c r="A269" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B269" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C269" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D269" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E269" t="s">
         <v>123</v>
@@ -17346,16 +17346,16 @@
     </row>
     <row r="270" spans="1:9">
       <c r="A270" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B270" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C270" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D270" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E270" t="s">
         <v>123</v>
@@ -17376,16 +17376,16 @@
     </row>
     <row r="271" spans="1:9">
       <c r="A271" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B271" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C271" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D271" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E271" t="s">
         <v>123</v>
@@ -17406,16 +17406,16 @@
     </row>
     <row r="272" spans="1:9">
       <c r="A272" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B272" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C272" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D272" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E272" t="s">
         <v>123</v>
@@ -17436,16 +17436,16 @@
     </row>
     <row r="273" spans="1:9">
       <c r="A273" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B273" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C273" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D273" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E273" t="s">
         <v>123</v>
@@ -17466,16 +17466,16 @@
     </row>
     <row r="274" spans="1:9">
       <c r="A274" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B274" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C274" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D274" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E274" t="s">
         <v>123</v>
@@ -17496,16 +17496,16 @@
     </row>
     <row r="275" spans="1:9">
       <c r="A275" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B275" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C275" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D275" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E275" t="s">
         <v>123</v>
@@ -17526,16 +17526,16 @@
     </row>
     <row r="276" spans="1:9">
       <c r="A276" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B276" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C276" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D276" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E276" t="s">
         <v>123</v>
@@ -17556,16 +17556,16 @@
     </row>
     <row r="277" spans="1:9">
       <c r="A277" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B277" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C277" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D277" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E277" t="s">
         <v>123</v>
@@ -17586,16 +17586,16 @@
     </row>
     <row r="278" spans="1:9">
       <c r="A278" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B278" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C278" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D278" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E278" t="s">
         <v>123</v>
@@ -17616,16 +17616,16 @@
     </row>
     <row r="279" spans="1:9">
       <c r="A279" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B279" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C279" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D279" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E279" t="s">
         <v>123</v>
@@ -17646,16 +17646,16 @@
     </row>
     <row r="280" spans="1:9">
       <c r="A280" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B280" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C280" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D280" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E280" t="s">
         <v>123</v>
@@ -17676,16 +17676,16 @@
     </row>
     <row r="281" spans="1:9">
       <c r="A281" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B281" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C281" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D281" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E281" t="s">
         <v>123</v>
@@ -17706,16 +17706,16 @@
     </row>
     <row r="282" spans="1:9">
       <c r="A282" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B282" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C282" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D282" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E282" t="s">
         <v>123</v>
@@ -17736,16 +17736,16 @@
     </row>
     <row r="283" spans="1:9">
       <c r="A283" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B283" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C283" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D283" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E283" t="s">
         <v>123</v>
@@ -17766,16 +17766,16 @@
     </row>
     <row r="284" spans="1:9">
       <c r="A284" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B284" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C284" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D284" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E284" t="s">
         <v>123</v>
@@ -17796,16 +17796,16 @@
     </row>
     <row r="285" spans="1:9">
       <c r="A285" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B285" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C285" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D285" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E285" t="s">
         <v>123</v>
@@ -17826,16 +17826,16 @@
     </row>
     <row r="286" spans="1:9">
       <c r="A286" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B286" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C286" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D286" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E286" t="s">
         <v>123</v>
@@ -17856,16 +17856,16 @@
     </row>
     <row r="287" spans="1:9">
       <c r="A287" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B287" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C287" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D287" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E287" t="s">
         <v>123</v>
@@ -17886,16 +17886,16 @@
     </row>
     <row r="288" spans="1:9">
       <c r="A288" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B288" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C288" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D288" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E288" t="s">
         <v>123</v>
@@ -17916,16 +17916,16 @@
     </row>
     <row r="289" spans="1:9">
       <c r="A289" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B289" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C289" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D289" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E289" t="s">
         <v>123</v>
@@ -17946,16 +17946,16 @@
     </row>
     <row r="290" spans="1:9">
       <c r="A290" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B290" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C290" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D290" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E290" t="s">
         <v>123</v>
@@ -17976,16 +17976,16 @@
     </row>
     <row r="291" spans="1:9">
       <c r="A291" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B291" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C291" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D291" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E291" t="s">
         <v>123</v>
@@ -18006,16 +18006,16 @@
     </row>
     <row r="292" spans="1:9">
       <c r="A292" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B292" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C292" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D292" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E292" t="s">
         <v>123</v>
@@ -18036,16 +18036,16 @@
     </row>
     <row r="293" spans="1:9">
       <c r="A293" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B293" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C293" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D293" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E293" t="s">
         <v>123</v>
@@ -18066,16 +18066,16 @@
     </row>
     <row r="294" spans="1:9">
       <c r="A294" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B294" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C294" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D294" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E294" t="s">
         <v>123</v>
@@ -18096,16 +18096,16 @@
     </row>
     <row r="295" spans="1:9">
       <c r="A295" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B295" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C295" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D295" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E295" t="s">
         <v>123</v>
@@ -18126,16 +18126,16 @@
     </row>
     <row r="296" spans="1:9">
       <c r="A296" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B296" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C296" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D296" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E296" t="s">
         <v>123</v>
@@ -18156,16 +18156,16 @@
     </row>
     <row r="297" spans="1:9">
       <c r="A297" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B297" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C297" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D297" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E297" t="s">
         <v>123</v>
@@ -18186,16 +18186,16 @@
     </row>
     <row r="298" spans="1:9">
       <c r="A298" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B298" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C298" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D298" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E298" t="s">
         <v>123</v>
@@ -18216,16 +18216,16 @@
     </row>
     <row r="299" spans="1:9">
       <c r="A299" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B299" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C299" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D299" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E299" t="s">
         <v>123</v>
@@ -18246,16 +18246,16 @@
     </row>
     <row r="300" spans="1:9">
       <c r="A300" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B300" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C300" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D300" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E300" t="s">
         <v>123</v>
@@ -18276,16 +18276,16 @@
     </row>
     <row r="301" spans="1:9">
       <c r="A301" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B301" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C301" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D301" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E301" t="s">
         <v>123</v>
@@ -18306,16 +18306,16 @@
     </row>
     <row r="302" spans="1:9">
       <c r="A302" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B302" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C302" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D302" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E302" t="s">
         <v>123</v>
@@ -18336,16 +18336,16 @@
     </row>
     <row r="303" spans="1:9">
       <c r="A303" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B303" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C303" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D303" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E303" t="s">
         <v>123</v>
@@ -18366,16 +18366,16 @@
     </row>
     <row r="304" spans="1:9">
       <c r="A304" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B304" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C304" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D304" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E304" t="s">
         <v>123</v>
@@ -18396,16 +18396,16 @@
     </row>
     <row r="305" spans="1:9">
       <c r="A305" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B305" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C305" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D305" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E305" t="s">
         <v>123</v>
@@ -18426,16 +18426,16 @@
     </row>
     <row r="306" spans="1:9">
       <c r="A306" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B306" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C306" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D306" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E306" t="s">
         <v>123</v>
@@ -18456,16 +18456,16 @@
     </row>
     <row r="307" spans="1:9">
       <c r="A307" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B307" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C307" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D307" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E307" t="s">
         <v>123</v>
@@ -18486,16 +18486,16 @@
     </row>
     <row r="308" spans="1:9">
       <c r="A308" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B308" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C308" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D308" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E308" t="s">
         <v>123</v>
@@ -18516,16 +18516,16 @@
     </row>
     <row r="309" spans="1:9">
       <c r="A309" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B309" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C309" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D309" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E309" t="s">
         <v>123</v>
@@ -18546,16 +18546,16 @@
     </row>
     <row r="310" spans="1:9">
       <c r="A310" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B310" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C310" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D310" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E310" t="s">
         <v>123</v>
@@ -18576,16 +18576,16 @@
     </row>
     <row r="311" spans="1:9">
       <c r="A311" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B311" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C311" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D311" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E311" t="s">
         <v>123</v>
@@ -18606,16 +18606,16 @@
     </row>
     <row r="312" spans="1:9">
       <c r="A312" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B312" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C312" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D312" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E312" t="s">
         <v>123</v>
@@ -18636,16 +18636,16 @@
     </row>
     <row r="313" spans="1:9">
       <c r="A313" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B313" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C313" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D313" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E313" t="s">
         <v>123</v>
@@ -18666,16 +18666,16 @@
     </row>
     <row r="314" spans="1:9">
       <c r="A314" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B314" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C314" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D314" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E314" t="s">
         <v>123</v>
@@ -28396,7 +28396,7 @@
         <v>4</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="K7" t="s">
         <v>121</v>
@@ -28687,7 +28687,7 @@
         <v>155</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="H23" t="s">
         <v>993</v>
@@ -28707,16 +28707,16 @@
         <v>6</v>
       </c>
       <c r="D24" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G24" t="s">
+        <v>1190</v>
+      </c>
+      <c r="K24" t="s">
+        <v>1191</v>
+      </c>
+      <c r="N24" t="s">
         <v>1193</v>
-      </c>
-      <c r="G24" t="s">
-        <v>1191</v>
-      </c>
-      <c r="K24" t="s">
-        <v>1192</v>
-      </c>
-      <c r="N24" t="s">
-        <v>1194</v>
       </c>
       <c r="Q24" t="s">
         <v>39</v>
@@ -28727,19 +28727,19 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="G25" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="H25" t="s">
+        <v>1194</v>
+      </c>
+      <c r="K25" t="s">
         <v>1195</v>
       </c>
-      <c r="K25" t="s">
+      <c r="N25" t="s">
         <v>1196</v>
-      </c>
-      <c r="N25" t="s">
-        <v>1197</v>
       </c>
       <c r="Q25" t="s">
         <v>39</v>

--- a/ReportDefs_vervestacks.xlsx
+++ b/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F3A4E89-1078-4789-AAB6-5EC0DD6CB6A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8D1148-D973-4A24-932E-902E87992E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28898" yWindow="-98" windowWidth="28996" windowHeight="15675" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenMap" sheetId="56" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5144" uniqueCount="1230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5153" uniqueCount="1233">
   <si>
     <t>Unit</t>
   </si>
@@ -3773,6 +3773,15 @@
   </si>
   <si>
     <t>Industrial</t>
+  </si>
+  <si>
+    <t>T_O_FuelJet_Int</t>
+  </si>
+  <si>
+    <t>JET</t>
+  </si>
+  <si>
+    <t>Int Aviation</t>
   </si>
 </sst>
 </file>
@@ -3981,7 +3990,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -3992,6 +4001,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="20">
@@ -7266,11 +7281,11 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10ADB714-E6AA-4E3E-B77B-62B65BA0E218}">
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.86328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.3984375" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="15.265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.46484375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.53125" bestFit="1" customWidth="1"/>
@@ -8235,7 +8250,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>1118</v>
       </c>
@@ -8246,7 +8261,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
         <v>1118</v>
       </c>
@@ -8257,7 +8272,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
         <v>1118</v>
       </c>
@@ -8268,7 +8283,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
         <v>1118</v>
       </c>
@@ -8279,7 +8294,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
         <v>1118</v>
       </c>
@@ -8290,7 +8305,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
         <v>1118</v>
       </c>
@@ -8301,7 +8316,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
         <v>1118</v>
       </c>
@@ -8312,7 +8327,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:6">
       <c r="A88" t="s">
         <v>1118</v>
       </c>
@@ -8323,7 +8338,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
         <v>1118</v>
       </c>
@@ -8334,7 +8349,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
         <v>1118</v>
       </c>
@@ -8345,7 +8360,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
         <v>1118</v>
       </c>
@@ -8355,60 +8370,62 @@
       <c r="D91" t="s">
         <v>1034</v>
       </c>
-    </row>
-    <row r="92" spans="1:4">
+      <c r="F91" s="10"/>
+    </row>
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>369</v>
+        <v>1118</v>
+      </c>
+      <c r="B92" s="10" t="s">
+        <v>1230</v>
       </c>
       <c r="C92" t="s">
-        <v>1037</v>
-      </c>
-      <c r="D92" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
+        <v>1232</v>
+      </c>
+      <c r="F92" s="10"/>
+    </row>
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
         <v>369</v>
       </c>
       <c r="C93" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="D93" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
       <c r="A94" t="s">
         <v>369</v>
       </c>
       <c r="C94" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="D94" t="s">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
       <c r="A95" t="s">
         <v>369</v>
       </c>
       <c r="C95" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="D95" t="s">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
       <c r="A96" t="s">
         <v>369</v>
       </c>
       <c r="C96" t="s">
-        <v>1229</v>
+        <v>1043</v>
       </c>
       <c r="D96" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -8416,10 +8433,10 @@
         <v>369</v>
       </c>
       <c r="C97" t="s">
-        <v>37</v>
+        <v>1229</v>
       </c>
       <c r="D97" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -8427,10 +8444,10 @@
         <v>369</v>
       </c>
       <c r="C98" t="s">
-        <v>1047</v>
+        <v>37</v>
       </c>
       <c r="D98" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -8438,10 +8455,10 @@
         <v>369</v>
       </c>
       <c r="C99" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="D99" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -8449,10 +8466,10 @@
         <v>369</v>
       </c>
       <c r="C100" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="D100" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -8460,10 +8477,10 @@
         <v>369</v>
       </c>
       <c r="C101" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D101" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -8471,10 +8488,10 @@
         <v>369</v>
       </c>
       <c r="C102" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D102" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -8482,10 +8499,10 @@
         <v>369</v>
       </c>
       <c r="C103" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="D103" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -8493,21 +8510,21 @@
         <v>369</v>
       </c>
       <c r="C104" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="D104" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>1119</v>
+        <v>369</v>
       </c>
       <c r="C105" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="D105" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -8515,10 +8532,10 @@
         <v>1119</v>
       </c>
       <c r="C106" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="D106" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -8526,10 +8543,10 @@
         <v>1119</v>
       </c>
       <c r="C107" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="D107" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -8537,10 +8554,10 @@
         <v>1119</v>
       </c>
       <c r="C108" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="D108" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -8548,10 +8565,10 @@
         <v>1119</v>
       </c>
       <c r="C109" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="D109" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -8559,10 +8576,10 @@
         <v>1119</v>
       </c>
       <c r="C110" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="D110" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -8570,10 +8587,10 @@
         <v>1119</v>
       </c>
       <c r="C111" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="D111" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -8581,10 +8598,10 @@
         <v>1119</v>
       </c>
       <c r="C112" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="D112" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -8592,10 +8609,10 @@
         <v>1119</v>
       </c>
       <c r="C113" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="D113" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -8603,10 +8620,10 @@
         <v>1119</v>
       </c>
       <c r="C114" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="D114" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -8614,10 +8631,10 @@
         <v>1119</v>
       </c>
       <c r="C115" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="D115" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -8625,10 +8642,10 @@
         <v>1119</v>
       </c>
       <c r="C116" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="D116" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -8636,10 +8653,10 @@
         <v>1119</v>
       </c>
       <c r="C117" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="D117" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -8647,10 +8664,10 @@
         <v>1119</v>
       </c>
       <c r="C118" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="D118" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -8658,10 +8675,10 @@
         <v>1119</v>
       </c>
       <c r="C119" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="D119" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -8669,10 +8686,10 @@
         <v>1119</v>
       </c>
       <c r="C120" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="D120" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -8680,10 +8697,10 @@
         <v>1119</v>
       </c>
       <c r="C121" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="D121" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -8691,10 +8708,10 @@
         <v>1119</v>
       </c>
       <c r="C122" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="D122" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -8702,10 +8719,10 @@
         <v>1119</v>
       </c>
       <c r="C123" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="D123" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -8713,10 +8730,10 @@
         <v>1119</v>
       </c>
       <c r="C124" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="D124" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -8724,10 +8741,10 @@
         <v>1119</v>
       </c>
       <c r="C125" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="D125" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -8735,10 +8752,10 @@
         <v>1119</v>
       </c>
       <c r="C126" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="D126" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -8746,10 +8763,10 @@
         <v>1119</v>
       </c>
       <c r="C127" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="D127" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -8757,10 +8774,10 @@
         <v>1119</v>
       </c>
       <c r="C128" t="s">
-        <v>1107</v>
+        <v>1101</v>
       </c>
       <c r="D128" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -8768,10 +8785,10 @@
         <v>1119</v>
       </c>
       <c r="C129" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="D129" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -8779,10 +8796,10 @@
         <v>1119</v>
       </c>
       <c r="C130" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="D130" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -8790,10 +8807,10 @@
         <v>1119</v>
       </c>
       <c r="C131" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="D131" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -8801,10 +8818,10 @@
         <v>1119</v>
       </c>
       <c r="C132" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="D132" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -8812,15 +8829,26 @@
         <v>1119</v>
       </c>
       <c r="C133" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D133" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C134" t="s">
         <v>1117</v>
       </c>
-      <c r="D133" t="s">
+      <c r="D134" t="s">
         <v>1116</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A72:D133">
-    <sortCondition ref="D72:D133"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A72:D134">
+    <sortCondition ref="D72:D134"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -28213,7 +28241,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:U26"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.86328125" bestFit="1" customWidth="1"/>
@@ -28745,6 +28773,26 @@
         <v>39</v>
       </c>
     </row>
+    <row r="26" spans="1:17">
+      <c r="A26" t="s">
+        <v>155</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>1230</v>
+      </c>
+      <c r="I26" t="s">
+        <v>1231</v>
+      </c>
+      <c r="K26" t="s">
+        <v>994</v>
+      </c>
+      <c r="N26" t="s">
+        <v>995</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>376</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="T4:U4"/>

--- a/ReportDefs_vervestacks.xlsx
+++ b/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8D1148-D973-4A24-932E-902E87992E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A5696F-CF95-489C-9B77-91F8A0AF2CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28898" yWindow="-98" windowWidth="28996" windowHeight="15675" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenMap" sheetId="56" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5153" uniqueCount="1233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5168" uniqueCount="1243">
   <si>
     <t>Unit</t>
   </si>
@@ -3782,6 +3782,36 @@
   </si>
   <si>
     <t>Int Aviation</t>
+  </si>
+  <si>
+    <t>T_P_Car</t>
+  </si>
+  <si>
+    <t>T_C_Car</t>
+  </si>
+  <si>
+    <t>T_F_MTrk</t>
+  </si>
+  <si>
+    <t>T_F_HTrk</t>
+  </si>
+  <si>
+    <t>T_F_VHTrk</t>
+  </si>
+  <si>
+    <t>Car/SUV</t>
+  </si>
+  <si>
+    <t>Van/Ute</t>
+  </si>
+  <si>
+    <t>Medium Trk</t>
+  </si>
+  <si>
+    <t>Heavy Trk</t>
+  </si>
+  <si>
+    <t>V Heavy Trk</t>
   </si>
 </sst>
 </file>
@@ -3999,14 +4029,14 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="18"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="19"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="20">
@@ -7281,7 +7311,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10ADB714-E6AA-4E3E-B77B-62B65BA0E218}">
-  <dimension ref="A1:G134"/>
+  <dimension ref="A1:G139"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.86328125" bestFit="1" customWidth="1"/>
@@ -8370,19 +8400,19 @@
       <c r="D91" t="s">
         <v>1034</v>
       </c>
-      <c r="F91" s="10"/>
+      <c r="F91" s="9"/>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
         <v>1118</v>
       </c>
-      <c r="B92" s="10" t="s">
+      <c r="B92" s="9" t="s">
         <v>1230</v>
       </c>
       <c r="C92" t="s">
         <v>1232</v>
       </c>
-      <c r="F92" s="10"/>
+      <c r="F92" s="9"/>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
@@ -8780,7 +8810,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="129" spans="1:4">
+    <row r="129" spans="1:6">
       <c r="A129" t="s">
         <v>1119</v>
       </c>
@@ -8791,7 +8821,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="130" spans="1:4">
+    <row r="130" spans="1:6">
       <c r="A130" t="s">
         <v>1119</v>
       </c>
@@ -8802,7 +8832,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="131" spans="1:4">
+    <row r="131" spans="1:6">
       <c r="A131" t="s">
         <v>1119</v>
       </c>
@@ -8813,7 +8843,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="132" spans="1:4">
+    <row r="132" spans="1:6">
       <c r="A132" t="s">
         <v>1119</v>
       </c>
@@ -8824,7 +8854,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="133" spans="1:4">
+    <row r="133" spans="1:6">
       <c r="A133" t="s">
         <v>1119</v>
       </c>
@@ -8835,7 +8865,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="134" spans="1:4">
+    <row r="134" spans="1:6">
       <c r="A134" t="s">
         <v>1119</v>
       </c>
@@ -8844,6 +8874,61 @@
       </c>
       <c r="D134" t="s">
         <v>1116</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C135" t="s">
+        <v>1239</v>
+      </c>
+      <c r="F135" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
+      <c r="A136" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C136" t="s">
+        <v>1238</v>
+      </c>
+      <c r="F136" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
+      <c r="A137" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C137" t="s">
+        <v>1240</v>
+      </c>
+      <c r="F137" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C138" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F138" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="A139" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C139" t="s">
+        <v>1242</v>
+      </c>
+      <c r="F139" t="s">
+        <v>1237</v>
       </c>
     </row>
   </sheetData>
@@ -28362,10 +28447,10 @@
       <c r="N4" t="s">
         <v>74</v>
       </c>
-      <c r="T4" s="8" t="s">
+      <c r="T4" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="U4" s="8"/>
+      <c r="U4" s="10"/>
     </row>
     <row r="5" spans="1:21">
       <c r="A5" t="s">
@@ -28777,7 +28862,7 @@
       <c r="A26" t="s">
         <v>155</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="8" t="s">
         <v>1230</v>
       </c>
       <c r="I26" t="s">

--- a/ReportDefs_vervestacks.xlsx
+++ b/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A5696F-CF95-489C-9B77-91F8A0AF2CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED56307-1871-4968-9324-4B0242C7726B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3585" yWindow="3585" windowWidth="21600" windowHeight="12683" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenMap" sheetId="56" r:id="rId1"/>
@@ -8881,7 +8881,7 @@
         <v>1119</v>
       </c>
       <c r="C135" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F135" t="s">
         <v>1233</v>
@@ -8892,7 +8892,7 @@
         <v>1119</v>
       </c>
       <c r="C136" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="F136" t="s">
         <v>1234</v>

--- a/ReportDefs_vervestacks.xlsx
+++ b/ReportDefs_vervestacks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED56307-1871-4968-9324-4B0242C7726B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2171F1-440D-4E72-B639-79C95AA40EEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="21600" windowHeight="12683" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenMap" sheetId="56" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5168" uniqueCount="1243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5174" uniqueCount="1244">
   <si>
     <t>Unit</t>
   </si>
@@ -3812,6 +3812,9 @@
   </si>
   <si>
     <t>V Heavy Trk</t>
+  </si>
+  <si>
+    <t>Tra_vehicles_new</t>
   </si>
 </sst>
 </file>
@@ -28326,7 +28329,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:U26"/>
+  <dimension ref="A1:U27"/>
   <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.86328125" bestFit="1" customWidth="1"/>
@@ -28860,21 +28863,41 @@
     </row>
     <row r="26" spans="1:17">
       <c r="A26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G26" t="s">
+        <v>1190</v>
+      </c>
+      <c r="K26" t="s">
+        <v>1191</v>
+      </c>
+      <c r="N26" t="s">
+        <v>1243</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27" t="s">
         <v>155</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D27" s="8" t="s">
         <v>1230</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I27" t="s">
         <v>1231</v>
       </c>
-      <c r="K26" t="s">
+      <c r="K27" t="s">
         <v>994</v>
       </c>
-      <c r="N26" t="s">
+      <c r="N27" t="s">
         <v>995</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="Q27" t="s">
         <v>376</v>
       </c>
     </row>
